--- a/data/c_vessel(容器).xlsx
+++ b/data/c_vessel(容器).xlsx
@@ -11,6 +11,9 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$G$1:$G$130</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -815,7 +818,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -823,12 +826,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1157,7 +1154,7 @@
     <col min="4" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="6" width="8.75" customWidth="1"/>
     <col min="7" max="7" width="10.875" customWidth="1"/>
-    <col min="10" max="10" width="19.375" customWidth="1"/>
+    <col min="10" max="11" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" spans="1:13">
@@ -1236,10 +1233,7 @@
       <c r="I3" s="1">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="str">
-        <f>_xlfn.CONCAT(B3,"-",D3)</f>
-        <v>1级容器-陶罐1</v>
-      </c>
+      <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="M3" s="2"/>
     </row>
@@ -1263,7 +1257,7 @@
         <v>10011</v>
       </c>
       <c r="G4" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -1271,10 +1265,7 @@
       <c r="I4" s="1">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="str">
-        <f t="shared" ref="J4:J35" si="0">_xlfn.CONCAT(B4,"-",D4)</f>
-        <v>1级容器-陶罐1</v>
-      </c>
+      <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1307,10 +1298,7 @@
       <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐1</v>
-      </c>
+      <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -1335,7 +1323,7 @@
         <v>10011</v>
       </c>
       <c r="G6" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -1343,10 +1331,7 @@
       <c r="I6" s="1">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐1</v>
-      </c>
+      <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -1379,10 +1364,7 @@
       <c r="I7" s="1">
         <v>1</v>
       </c>
-      <c r="J7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐2</v>
-      </c>
+      <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1407,7 +1389,7 @@
         <v>10021</v>
       </c>
       <c r="G8" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -1415,10 +1397,7 @@
       <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐2</v>
-      </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1451,10 +1430,7 @@
       <c r="I9" s="1">
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐2</v>
-      </c>
+      <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -1479,7 +1455,7 @@
         <v>10021</v>
       </c>
       <c r="G10" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
@@ -1487,10 +1463,7 @@
       <c r="I10" s="1">
         <v>1</v>
       </c>
-      <c r="J10" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐2</v>
-      </c>
+      <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -1523,10 +1496,7 @@
       <c r="I11" s="1">
         <v>1</v>
       </c>
-      <c r="J11" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐3</v>
-      </c>
+      <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -1551,7 +1521,7 @@
         <v>10031</v>
       </c>
       <c r="G12" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -1559,10 +1529,7 @@
       <c r="I12" s="1">
         <v>1</v>
       </c>
-      <c r="J12" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐3</v>
-      </c>
+      <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1595,10 +1562,7 @@
       <c r="I13" s="1">
         <v>1</v>
       </c>
-      <c r="J13" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐3</v>
-      </c>
+      <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -1623,7 +1587,7 @@
         <v>10031</v>
       </c>
       <c r="G14" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -1631,10 +1595,7 @@
       <c r="I14" s="1">
         <v>1</v>
       </c>
-      <c r="J14" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐3</v>
-      </c>
+      <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -1667,10 +1628,7 @@
       <c r="I15" s="1">
         <v>1</v>
       </c>
-      <c r="J15" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐4</v>
-      </c>
+      <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -1695,7 +1653,7 @@
         <v>10041</v>
       </c>
       <c r="G16" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -1703,10 +1661,7 @@
       <c r="I16" s="1">
         <v>1</v>
       </c>
-      <c r="J16" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐4</v>
-      </c>
+      <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1739,10 +1694,7 @@
       <c r="I17" s="1">
         <v>1</v>
       </c>
-      <c r="J17" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐4</v>
-      </c>
+      <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="1"/>
@@ -1767,7 +1719,7 @@
         <v>10041</v>
       </c>
       <c r="G18" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
@@ -1775,10 +1727,7 @@
       <c r="I18" s="1">
         <v>1</v>
       </c>
-      <c r="J18" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐4</v>
-      </c>
+      <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1811,10 +1760,7 @@
       <c r="I19" s="1">
         <v>1</v>
       </c>
-      <c r="J19" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐5</v>
-      </c>
+      <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -1839,7 +1785,7 @@
         <v>10051</v>
       </c>
       <c r="G20" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -1847,10 +1793,7 @@
       <c r="I20" s="1">
         <v>1</v>
       </c>
-      <c r="J20" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐5</v>
-      </c>
+      <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -1883,10 +1826,7 @@
       <c r="I21" s="1">
         <v>1</v>
       </c>
-      <c r="J21" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐5</v>
-      </c>
+      <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -1911,7 +1851,7 @@
         <v>10051</v>
       </c>
       <c r="G22" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -1919,10 +1859,7 @@
       <c r="I22" s="1">
         <v>1</v>
       </c>
-      <c r="J22" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐5</v>
-      </c>
+      <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1955,10 +1892,7 @@
       <c r="I23" s="1">
         <v>1</v>
       </c>
-      <c r="J23" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐6</v>
-      </c>
+      <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -1983,7 +1917,7 @@
         <v>10061</v>
       </c>
       <c r="G24" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
@@ -1991,10 +1925,7 @@
       <c r="I24" s="1">
         <v>1</v>
       </c>
-      <c r="J24" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐6</v>
-      </c>
+      <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -2027,10 +1958,7 @@
       <c r="I25" s="1">
         <v>1</v>
       </c>
-      <c r="J25" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐6</v>
-      </c>
+      <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2055,7 +1983,7 @@
         <v>10061</v>
       </c>
       <c r="G26" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
@@ -2063,10 +1991,7 @@
       <c r="I26" s="1">
         <v>1</v>
       </c>
-      <c r="J26" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-陶罐6</v>
-      </c>
+      <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2099,10 +2024,7 @@
       <c r="I27" s="1">
         <v>1</v>
       </c>
-      <c r="J27" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-稻草人</v>
-      </c>
+      <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -2127,7 +2049,7 @@
         <v>10071</v>
       </c>
       <c r="G28" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H28" s="1">
         <v>1</v>
@@ -2135,10 +2057,7 @@
       <c r="I28" s="1">
         <v>1</v>
       </c>
-      <c r="J28" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-稻草人</v>
-      </c>
+      <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -2171,10 +2090,7 @@
       <c r="I29" s="1">
         <v>1</v>
       </c>
-      <c r="J29" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-稻草人</v>
-      </c>
+      <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -2199,7 +2115,7 @@
         <v>10071</v>
       </c>
       <c r="G30" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
@@ -2207,10 +2123,7 @@
       <c r="I30" s="1">
         <v>1</v>
       </c>
-      <c r="J30" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-稻草人</v>
-      </c>
+      <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -2243,10 +2156,7 @@
       <c r="I31" s="1">
         <v>1</v>
       </c>
-      <c r="J31" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-魔物尸体</v>
-      </c>
+      <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -2271,7 +2181,7 @@
         <v>10081</v>
       </c>
       <c r="G32" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
@@ -2279,10 +2189,7 @@
       <c r="I32" s="1">
         <v>1</v>
       </c>
-      <c r="J32" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-魔物尸体</v>
-      </c>
+      <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -2315,10 +2222,7 @@
       <c r="I33" s="1">
         <v>1</v>
       </c>
-      <c r="J33" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-魔物尸体</v>
-      </c>
+      <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -2343,7 +2247,7 @@
         <v>10081</v>
       </c>
       <c r="G34" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
@@ -2351,10 +2255,7 @@
       <c r="I34" s="1">
         <v>1</v>
       </c>
-      <c r="J34" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-魔物尸体</v>
-      </c>
+      <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -2387,10 +2288,7 @@
       <c r="I35" s="1">
         <v>1</v>
       </c>
-      <c r="J35" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>1级容器-沙袋</v>
-      </c>
+      <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -2415,7 +2313,7 @@
         <v>10091</v>
       </c>
       <c r="G36" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H36" s="1">
         <v>1</v>
@@ -2423,10 +2321,7 @@
       <c r="I36" s="1">
         <v>1</v>
       </c>
-      <c r="J36" s="2" t="str">
-        <f t="shared" ref="J36:J67" si="1">_xlfn.CONCAT(B36,"-",D36)</f>
-        <v>1级容器-沙袋</v>
-      </c>
+      <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -2459,10 +2354,7 @@
       <c r="I37" s="1">
         <v>1</v>
       </c>
-      <c r="J37" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>1级容器-沙袋</v>
-      </c>
+      <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -2487,7 +2379,7 @@
         <v>10091</v>
       </c>
       <c r="G38" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
@@ -2495,10 +2387,7 @@
       <c r="I38" s="1">
         <v>1</v>
       </c>
-      <c r="J38" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>1级容器-沙袋</v>
-      </c>
+      <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -2531,10 +2420,7 @@
       <c r="I39" s="1">
         <v>1</v>
       </c>
-      <c r="J39" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>1级容器-推车木箱</v>
-      </c>
+      <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -2559,7 +2445,7 @@
         <v>10101</v>
       </c>
       <c r="G40" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
@@ -2567,10 +2453,7 @@
       <c r="I40" s="1">
         <v>1</v>
       </c>
-      <c r="J40" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>1级容器-推车木箱</v>
-      </c>
+      <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
@@ -2603,10 +2486,7 @@
       <c r="I41" s="1">
         <v>1</v>
       </c>
-      <c r="J41" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>1级容器-推车木箱</v>
-      </c>
+      <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -2631,7 +2511,7 @@
         <v>10101</v>
       </c>
       <c r="G42" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H42" s="1">
         <v>1</v>
@@ -2639,10 +2519,7 @@
       <c r="I42" s="1">
         <v>1</v>
       </c>
-      <c r="J42" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>1级容器-推车木箱</v>
-      </c>
+      <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -2675,10 +2552,7 @@
       <c r="I43" s="1">
         <v>1</v>
       </c>
-      <c r="J43" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-炼金材料箱</v>
-      </c>
+      <c r="J43" s="2"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -2703,7 +2577,7 @@
         <v>20011</v>
       </c>
       <c r="G44" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H44" s="1">
         <v>1</v>
@@ -2711,10 +2585,7 @@
       <c r="I44" s="1">
         <v>1</v>
       </c>
-      <c r="J44" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-炼金材料箱</v>
-      </c>
+      <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -2747,10 +2618,7 @@
       <c r="I45" s="1">
         <v>1</v>
       </c>
-      <c r="J45" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-炼金材料箱</v>
-      </c>
+      <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -2775,7 +2643,7 @@
         <v>20011</v>
       </c>
       <c r="G46" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H46" s="1">
         <v>1</v>
@@ -2783,10 +2651,7 @@
       <c r="I46" s="1">
         <v>1</v>
       </c>
-      <c r="J46" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-炼金材料箱</v>
-      </c>
+      <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -2819,10 +2684,7 @@
       <c r="I47" s="1">
         <v>1</v>
       </c>
-      <c r="J47" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-杂物柜</v>
-      </c>
+      <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -2847,7 +2709,7 @@
         <v>20021</v>
       </c>
       <c r="G48" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H48" s="1">
         <v>1</v>
@@ -2855,10 +2717,7 @@
       <c r="I48" s="1">
         <v>1</v>
       </c>
-      <c r="J48" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-杂物柜</v>
-      </c>
+      <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -2891,10 +2750,7 @@
       <c r="I49" s="1">
         <v>1</v>
       </c>
-      <c r="J49" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-杂物柜</v>
-      </c>
+      <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -2919,7 +2775,7 @@
         <v>20021</v>
       </c>
       <c r="G50" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H50" s="1">
         <v>1</v>
@@ -2927,10 +2783,7 @@
       <c r="I50" s="1">
         <v>1</v>
       </c>
-      <c r="J50" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-杂物柜</v>
-      </c>
+      <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -2963,10 +2816,7 @@
       <c r="I51" s="1">
         <v>1</v>
       </c>
-      <c r="J51" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-酒桶</v>
-      </c>
+      <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -2991,7 +2841,7 @@
         <v>20031</v>
       </c>
       <c r="G52" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H52" s="1">
         <v>1</v>
@@ -2999,10 +2849,7 @@
       <c r="I52" s="1">
         <v>1</v>
       </c>
-      <c r="J52" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-酒桶</v>
-      </c>
+      <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -3027,7 +2874,7 @@
         <v>20031</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H53" s="1">
         <v>1</v>
@@ -3035,10 +2882,7 @@
       <c r="I53" s="1">
         <v>1</v>
       </c>
-      <c r="J53" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-酒桶</v>
-      </c>
+      <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -3063,7 +2907,7 @@
         <v>20031</v>
       </c>
       <c r="G54" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H54" s="1">
         <v>1</v>
@@ -3071,10 +2915,7 @@
       <c r="I54" s="1">
         <v>1</v>
       </c>
-      <c r="J54" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-酒桶</v>
-      </c>
+      <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -3107,10 +2948,7 @@
       <c r="I55" s="1">
         <v>1</v>
       </c>
-      <c r="J55" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-工具箱</v>
-      </c>
+      <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -3135,7 +2973,7 @@
         <v>20041</v>
       </c>
       <c r="G56" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H56" s="1">
         <v>1</v>
@@ -3143,10 +2981,7 @@
       <c r="I56" s="1">
         <v>1</v>
       </c>
-      <c r="J56" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-工具箱</v>
-      </c>
+      <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -3171,7 +3006,7 @@
         <v>20041</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H57" s="1">
         <v>1</v>
@@ -3179,10 +3014,7 @@
       <c r="I57" s="1">
         <v>1</v>
       </c>
-      <c r="J57" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-工具箱</v>
-      </c>
+      <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -3207,7 +3039,7 @@
         <v>20041</v>
       </c>
       <c r="G58" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H58" s="1">
         <v>1</v>
@@ -3215,10 +3047,7 @@
       <c r="I58" s="1">
         <v>1</v>
       </c>
-      <c r="J58" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-工具箱</v>
-      </c>
+      <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -3251,10 +3080,7 @@
       <c r="I59" s="1">
         <v>1</v>
       </c>
-      <c r="J59" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-法师长袍</v>
-      </c>
+      <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -3279,7 +3105,7 @@
         <v>20051</v>
       </c>
       <c r="G60" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H60" s="1">
         <v>1</v>
@@ -3287,10 +3113,7 @@
       <c r="I60" s="1">
         <v>1</v>
       </c>
-      <c r="J60" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-法师长袍</v>
-      </c>
+      <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -3315,7 +3138,7 @@
         <v>20051</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H61" s="1">
         <v>1</v>
@@ -3323,10 +3146,7 @@
       <c r="I61" s="1">
         <v>1</v>
       </c>
-      <c r="J61" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-法师长袍</v>
-      </c>
+      <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -3351,7 +3171,7 @@
         <v>20051</v>
       </c>
       <c r="G62" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H62" s="1">
         <v>1</v>
@@ -3359,10 +3179,7 @@
       <c r="I62" s="1">
         <v>1</v>
       </c>
-      <c r="J62" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-法师长袍</v>
-      </c>
+      <c r="J62" s="2"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -3395,10 +3212,7 @@
       <c r="I63" s="1">
         <v>1</v>
       </c>
-      <c r="J63" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-战士盔甲</v>
-      </c>
+      <c r="J63" s="2"/>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -3423,7 +3237,7 @@
         <v>20061</v>
       </c>
       <c r="G64" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H64" s="1">
         <v>1</v>
@@ -3431,10 +3245,7 @@
       <c r="I64" s="1">
         <v>1</v>
       </c>
-      <c r="J64" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-战士盔甲</v>
-      </c>
+      <c r="J64" s="2"/>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -3459,7 +3270,7 @@
         <v>20061</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
@@ -3467,10 +3278,7 @@
       <c r="I65" s="1">
         <v>1</v>
       </c>
-      <c r="J65" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-战士盔甲</v>
-      </c>
+      <c r="J65" s="2"/>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -3495,7 +3303,7 @@
         <v>20061</v>
       </c>
       <c r="G66" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H66" s="1">
         <v>1</v>
@@ -3503,10 +3311,7 @@
       <c r="I66" s="1">
         <v>1</v>
       </c>
-      <c r="J66" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-战士盔甲</v>
-      </c>
+      <c r="J66" s="2"/>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -3539,10 +3344,7 @@
       <c r="I67" s="1">
         <v>1</v>
       </c>
-      <c r="J67" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>2级容器-普通储物箱</v>
-      </c>
+      <c r="J67" s="2"/>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -3567,7 +3369,7 @@
         <v>20071</v>
       </c>
       <c r="G68" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
@@ -3575,10 +3377,7 @@
       <c r="I68" s="1">
         <v>1</v>
       </c>
-      <c r="J68" s="2" t="str">
-        <f t="shared" ref="J68:J99" si="2">_xlfn.CONCAT(B68,"-",D68)</f>
-        <v>2级容器-普通储物箱</v>
-      </c>
+      <c r="J68" s="2"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -3611,10 +3410,7 @@
       <c r="I69" s="1">
         <v>1</v>
       </c>
-      <c r="J69" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>2级容器-普通储物箱</v>
-      </c>
+      <c r="J69" s="2"/>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -3639,7 +3435,7 @@
         <v>20071</v>
       </c>
       <c r="G70" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H70" s="1">
         <v>1</v>
@@ -3647,10 +3443,7 @@
       <c r="I70" s="1">
         <v>1</v>
       </c>
-      <c r="J70" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>2级容器-普通储物箱</v>
-      </c>
+      <c r="J70" s="2"/>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -3683,10 +3476,7 @@
       <c r="I71" s="1">
         <v>1</v>
       </c>
-      <c r="J71" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>2级容器-损坏的马车</v>
-      </c>
+      <c r="J71" s="2"/>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -3711,7 +3501,7 @@
         <v>20081</v>
       </c>
       <c r="G72" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H72" s="1">
         <v>1</v>
@@ -3719,10 +3509,7 @@
       <c r="I72" s="1">
         <v>1</v>
       </c>
-      <c r="J72" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>2级容器-损坏的马车</v>
-      </c>
+      <c r="J72" s="2"/>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -3755,10 +3542,7 @@
       <c r="I73" s="1">
         <v>1</v>
       </c>
-      <c r="J73" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>2级容器-损坏的马车</v>
-      </c>
+      <c r="J73" s="2"/>
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -3783,7 +3567,7 @@
         <v>20081</v>
       </c>
       <c r="G74" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H74" s="1">
         <v>1</v>
@@ -3791,10 +3575,7 @@
       <c r="I74" s="1">
         <v>1</v>
       </c>
-      <c r="J74" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>2级容器-损坏的马车</v>
-      </c>
+      <c r="J74" s="2"/>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -3827,10 +3608,7 @@
       <c r="I75" s="1">
         <v>1</v>
       </c>
-      <c r="J75" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-手提箱</v>
-      </c>
+      <c r="J75" s="2"/>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -3855,7 +3633,7 @@
         <v>30012</v>
       </c>
       <c r="G76" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H76" s="1">
         <v>1</v>
@@ -3863,10 +3641,7 @@
       <c r="I76" s="1">
         <v>1</v>
       </c>
-      <c r="J76" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-手提箱</v>
-      </c>
+      <c r="J76" s="2"/>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -3890,8 +3665,8 @@
       <c r="F77" s="3">
         <v>30012</v>
       </c>
-      <c r="G77" s="3">
-        <v>0</v>
+      <c r="G77" s="1">
+        <v>5000</v>
       </c>
       <c r="H77" s="3">
         <v>1</v>
@@ -3899,10 +3674,7 @@
       <c r="I77" s="3">
         <v>1</v>
       </c>
-      <c r="J77" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-手提箱</v>
-      </c>
+      <c r="J77" s="4"/>
       <c r="K77" s="4"/>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -3927,7 +3699,7 @@
         <v>30011</v>
       </c>
       <c r="G78" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H78" s="3">
         <v>1</v>
@@ -3935,10 +3707,7 @@
       <c r="I78" s="3">
         <v>1</v>
       </c>
-      <c r="J78" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-手提箱</v>
-      </c>
+      <c r="J78" s="4"/>
       <c r="K78" s="4"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -3953,28 +3722,25 @@
       <c r="C79" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E79" s="5">
+      <c r="E79" s="3">
         <v>3002</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="3">
         <v>30023</v>
       </c>
-      <c r="G79" s="5">
+      <c r="G79" s="3">
         <v>10000</v>
       </c>
-      <c r="H79" s="5">
-        <v>1</v>
-      </c>
-      <c r="I79" s="5">
-        <v>1</v>
-      </c>
-      <c r="J79" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-武器箱</v>
-      </c>
+      <c r="H79" s="3">
+        <v>1</v>
+      </c>
+      <c r="I79" s="3">
+        <v>1</v>
+      </c>
+      <c r="J79" s="4"/>
       <c r="K79" s="4"/>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -3989,28 +3755,25 @@
       <c r="C80" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E80" s="3">
         <v>3002</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="3">
         <v>30022</v>
       </c>
-      <c r="G80" s="5">
-        <v>5000</v>
-      </c>
-      <c r="H80" s="5">
-        <v>1</v>
-      </c>
-      <c r="I80" s="5">
-        <v>1</v>
-      </c>
-      <c r="J80" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-武器箱</v>
-      </c>
+      <c r="G80" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H80" s="3">
+        <v>1</v>
+      </c>
+      <c r="I80" s="3">
+        <v>1</v>
+      </c>
+      <c r="J80" s="4"/>
       <c r="K80" s="4"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -4025,28 +3788,25 @@
       <c r="C81" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D81" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="3">
         <v>3002</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="3">
         <v>30022</v>
       </c>
-      <c r="G81" s="5">
+      <c r="G81" s="3">
         <v>0</v>
       </c>
-      <c r="H81" s="5">
-        <v>1</v>
-      </c>
-      <c r="I81" s="5">
-        <v>1</v>
-      </c>
-      <c r="J81" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-武器箱</v>
-      </c>
+      <c r="H81" s="3">
+        <v>1</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1</v>
+      </c>
+      <c r="J81" s="4"/>
       <c r="K81" s="4"/>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -4061,28 +3821,25 @@
       <c r="C82" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E82" s="5">
+      <c r="E82" s="3">
         <v>3002</v>
       </c>
-      <c r="F82" s="5">
+      <c r="F82" s="3">
         <v>30021</v>
       </c>
-      <c r="G82" s="5">
-        <v>2500</v>
-      </c>
-      <c r="H82" s="5">
-        <v>1</v>
-      </c>
-      <c r="I82" s="5">
-        <v>1</v>
-      </c>
-      <c r="J82" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-武器箱</v>
-      </c>
+      <c r="G82" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H82" s="3">
+        <v>1</v>
+      </c>
+      <c r="I82" s="3">
+        <v>1</v>
+      </c>
+      <c r="J82" s="4"/>
       <c r="K82" s="4"/>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -4115,10 +3872,7 @@
       <c r="I83" s="3">
         <v>1</v>
       </c>
-      <c r="J83" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-魔晶核包</v>
-      </c>
+      <c r="J83" s="4"/>
       <c r="K83" s="4"/>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -4143,7 +3897,7 @@
         <v>30032</v>
       </c>
       <c r="G84" s="3">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H84" s="3">
         <v>1</v>
@@ -4151,10 +3905,7 @@
       <c r="I84" s="3">
         <v>1</v>
       </c>
-      <c r="J84" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-魔晶核包</v>
-      </c>
+      <c r="J84" s="4"/>
       <c r="K84" s="4"/>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -4187,10 +3938,7 @@
       <c r="I85" s="3">
         <v>1</v>
       </c>
-      <c r="J85" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-魔晶核包</v>
-      </c>
+      <c r="J85" s="4"/>
       <c r="K85" s="4"/>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -4215,7 +3963,7 @@
         <v>30031</v>
       </c>
       <c r="G86" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H86" s="1">
         <v>1</v>
@@ -4223,10 +3971,7 @@
       <c r="I86" s="1">
         <v>1</v>
       </c>
-      <c r="J86" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-魔晶核包</v>
-      </c>
+      <c r="J86" s="2"/>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -4259,10 +4004,7 @@
       <c r="I87" s="1">
         <v>1</v>
       </c>
-      <c r="J87" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-医疗包</v>
-      </c>
+      <c r="J87" s="2"/>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -4287,7 +4029,7 @@
         <v>30042</v>
       </c>
       <c r="G88" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H88" s="1">
         <v>1</v>
@@ -4295,10 +4037,7 @@
       <c r="I88" s="1">
         <v>1</v>
       </c>
-      <c r="J88" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-医疗包</v>
-      </c>
+      <c r="J88" s="2"/>
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -4331,10 +4070,7 @@
       <c r="I89" s="1">
         <v>1</v>
       </c>
-      <c r="J89" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-医疗包</v>
-      </c>
+      <c r="J89" s="2"/>
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -4359,7 +4095,7 @@
         <v>30041</v>
       </c>
       <c r="G90" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H90" s="1">
         <v>1</v>
@@ -4367,10 +4103,7 @@
       <c r="I90" s="1">
         <v>1</v>
       </c>
-      <c r="J90" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-医疗包</v>
-      </c>
+      <c r="J90" s="2"/>
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -4403,10 +4136,7 @@
       <c r="I91" s="1">
         <v>1</v>
       </c>
-      <c r="J91" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-旅行包</v>
-      </c>
+      <c r="J91" s="2"/>
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -4431,7 +4161,7 @@
         <v>30052</v>
       </c>
       <c r="G92" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H92" s="1">
         <v>1</v>
@@ -4439,10 +4169,7 @@
       <c r="I92" s="1">
         <v>1</v>
       </c>
-      <c r="J92" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-旅行包</v>
-      </c>
+      <c r="J92" s="2"/>
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -4467,7 +4194,7 @@
         <v>30052</v>
       </c>
       <c r="G93" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H93" s="1">
         <v>1</v>
@@ -4475,10 +4202,7 @@
       <c r="I93" s="1">
         <v>1</v>
       </c>
-      <c r="J93" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-旅行包</v>
-      </c>
+      <c r="J93" s="2"/>
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -4503,7 +4227,7 @@
         <v>30051</v>
       </c>
       <c r="G94" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H94" s="1">
         <v>1</v>
@@ -4511,10 +4235,7 @@
       <c r="I94" s="1">
         <v>1</v>
       </c>
-      <c r="J94" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-旅行包</v>
-      </c>
+      <c r="J94" s="2"/>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -4547,10 +4268,7 @@
       <c r="I95" s="1">
         <v>1</v>
       </c>
-      <c r="J95" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-炼金炉</v>
-      </c>
+      <c r="J95" s="2"/>
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -4575,7 +4293,7 @@
         <v>30062</v>
       </c>
       <c r="G96" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H96" s="1">
         <v>1</v>
@@ -4583,10 +4301,7 @@
       <c r="I96" s="1">
         <v>1</v>
       </c>
-      <c r="J96" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-炼金炉</v>
-      </c>
+      <c r="J96" s="2"/>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -4619,10 +4334,7 @@
       <c r="I97" s="1">
         <v>1</v>
       </c>
-      <c r="J97" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-炼金炉</v>
-      </c>
+      <c r="J97" s="2"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -4647,7 +4359,7 @@
         <v>30061</v>
       </c>
       <c r="G98" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H98" s="1">
         <v>1</v>
@@ -4655,10 +4367,7 @@
       <c r="I98" s="1">
         <v>1</v>
       </c>
-      <c r="J98" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3级容器-炼金炉</v>
-      </c>
+      <c r="J98" s="2"/>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -4691,10 +4400,7 @@
       <c r="I99" s="1">
         <v>1</v>
       </c>
-      <c r="J99" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>4级容器-高级储物箱</v>
-      </c>
+      <c r="J99" s="2"/>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -4719,7 +4425,7 @@
         <v>40013</v>
       </c>
       <c r="G100" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H100" s="1">
         <v>1</v>
@@ -4727,10 +4433,7 @@
       <c r="I100" s="1">
         <v>1</v>
       </c>
-      <c r="J100" s="2" t="str">
-        <f t="shared" ref="J100:J130" si="3">_xlfn.CONCAT(B100,"-",D100)</f>
-        <v>4级容器-高级储物箱</v>
-      </c>
+      <c r="J100" s="2"/>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -4763,10 +4466,7 @@
       <c r="I101" s="1">
         <v>1</v>
       </c>
-      <c r="J101" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-高级储物箱</v>
-      </c>
+      <c r="J101" s="2"/>
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -4791,7 +4491,7 @@
         <v>40012</v>
       </c>
       <c r="G102" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H102" s="1">
         <v>1</v>
@@ -4799,10 +4499,7 @@
       <c r="I102" s="1">
         <v>1</v>
       </c>
-      <c r="J102" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-高级储物箱</v>
-      </c>
+      <c r="J102" s="2"/>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -4835,10 +4532,7 @@
       <c r="I103" s="1">
         <v>1</v>
       </c>
-      <c r="J103" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-高级旅行包</v>
-      </c>
+      <c r="J103" s="2"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -4863,7 +4557,7 @@
         <v>40023</v>
       </c>
       <c r="G104" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H104" s="1">
         <v>1</v>
@@ -4871,10 +4565,7 @@
       <c r="I104" s="1">
         <v>1</v>
       </c>
-      <c r="J104" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-高级旅行包</v>
-      </c>
+      <c r="J104" s="2"/>
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -4899,7 +4590,7 @@
         <v>40023</v>
       </c>
       <c r="G105" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H105" s="1">
         <v>1</v>
@@ -4907,10 +4598,7 @@
       <c r="I105" s="1">
         <v>1</v>
       </c>
-      <c r="J105" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-高级旅行包</v>
-      </c>
+      <c r="J105" s="2"/>
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -4935,7 +4623,7 @@
         <v>40022</v>
       </c>
       <c r="G106" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H106" s="1">
         <v>1</v>
@@ -4943,10 +4631,7 @@
       <c r="I106" s="1">
         <v>1</v>
       </c>
-      <c r="J106" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-高级旅行包</v>
-      </c>
+      <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -4979,10 +4664,7 @@
       <c r="I107" s="1">
         <v>1</v>
       </c>
-      <c r="J107" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-魔法材料柜</v>
-      </c>
+      <c r="J107" s="2"/>
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -5007,7 +4689,7 @@
         <v>40033</v>
       </c>
       <c r="G108" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H108" s="1">
         <v>1</v>
@@ -5015,10 +4697,7 @@
       <c r="I108" s="1">
         <v>1</v>
       </c>
-      <c r="J108" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-魔法材料柜</v>
-      </c>
+      <c r="J108" s="2"/>
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -5051,10 +4730,7 @@
       <c r="I109" s="1">
         <v>1</v>
       </c>
-      <c r="J109" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-魔法材料柜</v>
-      </c>
+      <c r="J109" s="2"/>
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -5079,7 +4755,7 @@
         <v>40032</v>
       </c>
       <c r="G110" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H110" s="1">
         <v>1</v>
@@ -5087,10 +4763,7 @@
       <c r="I110" s="1">
         <v>1</v>
       </c>
-      <c r="J110" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-魔法材料柜</v>
-      </c>
+      <c r="J110" s="2"/>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -5123,10 +4796,7 @@
       <c r="I111" s="1">
         <v>1</v>
       </c>
-      <c r="J111" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-魔晶核箱</v>
-      </c>
+      <c r="J111" s="2"/>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -5151,7 +4821,7 @@
         <v>40043</v>
       </c>
       <c r="G112" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H112" s="1">
         <v>1</v>
@@ -5159,10 +4829,7 @@
       <c r="I112" s="1">
         <v>1</v>
       </c>
-      <c r="J112" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-魔晶核箱</v>
-      </c>
+      <c r="J112" s="2"/>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -5195,10 +4862,7 @@
       <c r="I113" s="1">
         <v>1</v>
       </c>
-      <c r="J113" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-魔晶核箱</v>
-      </c>
+      <c r="J113" s="2"/>
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -5223,7 +4887,7 @@
         <v>40042</v>
       </c>
       <c r="G114" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H114" s="1">
         <v>1</v>
@@ -5231,10 +4895,7 @@
       <c r="I114" s="1">
         <v>1</v>
       </c>
-      <c r="J114" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-魔晶核箱</v>
-      </c>
+      <c r="J114" s="2"/>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -5267,10 +4928,7 @@
       <c r="I115" s="1">
         <v>1</v>
       </c>
-      <c r="J115" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-医疗箱</v>
-      </c>
+      <c r="J115" s="2"/>
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -5295,7 +4953,7 @@
         <v>40053</v>
       </c>
       <c r="G116" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H116" s="1">
         <v>1</v>
@@ -5303,10 +4961,7 @@
       <c r="I116" s="1">
         <v>1</v>
       </c>
-      <c r="J116" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-医疗箱</v>
-      </c>
+      <c r="J116" s="2"/>
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -5339,10 +4994,7 @@
       <c r="I117" s="1">
         <v>1</v>
       </c>
-      <c r="J117" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-医疗箱</v>
-      </c>
+      <c r="J117" s="2"/>
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -5367,7 +5019,7 @@
         <v>40052</v>
       </c>
       <c r="G118" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H118" s="1">
         <v>1</v>
@@ -5375,10 +5027,7 @@
       <c r="I118" s="1">
         <v>1</v>
       </c>
-      <c r="J118" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4级容器-医疗箱</v>
-      </c>
+      <c r="J118" s="2"/>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -5411,10 +5060,7 @@
       <c r="I119" s="1">
         <v>1</v>
       </c>
-      <c r="J119" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>5级容器-小保险箱</v>
-      </c>
+      <c r="J119" s="2"/>
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -5439,7 +5085,7 @@
         <v>50014</v>
       </c>
       <c r="G120" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H120" s="1">
         <v>1</v>
@@ -5447,10 +5093,7 @@
       <c r="I120" s="1">
         <v>1</v>
       </c>
-      <c r="J120" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>5级容器-小保险箱</v>
-      </c>
+      <c r="J120" s="2"/>
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -5483,10 +5126,7 @@
       <c r="I121" s="1">
         <v>1</v>
       </c>
-      <c r="J121" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>5级容器-小保险箱</v>
-      </c>
+      <c r="J121" s="2"/>
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -5511,7 +5151,7 @@
         <v>50013</v>
       </c>
       <c r="G122" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H122" s="1">
         <v>1</v>
@@ -5519,10 +5159,7 @@
       <c r="I122" s="1">
         <v>1</v>
       </c>
-      <c r="J122" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>5级容器-小保险箱</v>
-      </c>
+      <c r="J122" s="2"/>
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -5537,16 +5174,16 @@
       <c r="C123" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="D123" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E123" s="7">
+      <c r="E123" s="5">
         <v>5002</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F123" s="5">
         <v>50025</v>
       </c>
-      <c r="G123" s="7">
+      <c r="G123" s="5">
         <v>10000</v>
       </c>
       <c r="H123" s="1">
@@ -5555,10 +5192,7 @@
       <c r="I123" s="1">
         <v>1</v>
       </c>
-      <c r="J123" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>5级容器-魔法仪器</v>
-      </c>
+      <c r="J123" s="2"/>
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -5573,16 +5207,16 @@
       <c r="C124" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D124" s="7" t="s">
+      <c r="D124" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E124" s="7">
+      <c r="E124" s="5">
         <v>5002</v>
       </c>
-      <c r="F124" s="7">
+      <c r="F124" s="5">
         <v>50024</v>
       </c>
-      <c r="G124" s="7">
+      <c r="G124" s="5">
         <v>0</v>
       </c>
       <c r="H124" s="1">
@@ -5591,10 +5225,7 @@
       <c r="I124" s="1">
         <v>1</v>
       </c>
-      <c r="J124" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>5级容器-魔法仪器</v>
-      </c>
+      <c r="J124" s="2"/>
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -5609,16 +5240,16 @@
       <c r="C125" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="D125" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E125" s="7">
+      <c r="E125" s="5">
         <v>5002</v>
       </c>
-      <c r="F125" s="7">
+      <c r="F125" s="5">
         <v>50024</v>
       </c>
-      <c r="G125" s="7">
+      <c r="G125" s="5">
         <v>0</v>
       </c>
       <c r="H125" s="1">
@@ -5627,10 +5258,7 @@
       <c r="I125" s="1">
         <v>1</v>
       </c>
-      <c r="J125" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>5级容器-魔法仪器</v>
-      </c>
+      <c r="J125" s="2"/>
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -5645,16 +5273,16 @@
       <c r="C126" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="D126" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E126" s="7">
+      <c r="E126" s="5">
         <v>5002</v>
       </c>
-      <c r="F126" s="7">
+      <c r="F126" s="5">
         <v>50023</v>
       </c>
-      <c r="G126" s="7">
+      <c r="G126" s="5">
         <v>0</v>
       </c>
       <c r="H126" s="1">
@@ -5663,10 +5291,7 @@
       <c r="I126" s="1">
         <v>1</v>
       </c>
-      <c r="J126" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>5级容器-魔法仪器</v>
-      </c>
+      <c r="J126" s="2"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -5699,10 +5324,7 @@
       <c r="I127" s="1">
         <v>1</v>
       </c>
-      <c r="J127" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>6级容器-保险柜</v>
-      </c>
+      <c r="J127" s="2"/>
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -5727,7 +5349,7 @@
         <v>60015</v>
       </c>
       <c r="G128" s="1">
-        <v>5000</v>
+        <v>6600</v>
       </c>
       <c r="H128" s="1">
         <v>1</v>
@@ -5735,10 +5357,7 @@
       <c r="I128" s="1">
         <v>1</v>
       </c>
-      <c r="J128" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>6级容器-保险柜</v>
-      </c>
+      <c r="J128" s="2"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -5771,10 +5390,7 @@
       <c r="I129" s="1">
         <v>1</v>
       </c>
-      <c r="J129" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>6级容器-保险柜</v>
-      </c>
+      <c r="J129" s="2"/>
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -5799,7 +5415,7 @@
         <v>60014</v>
       </c>
       <c r="G130" s="1">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H130" s="1">
         <v>1</v>
@@ -5807,15 +5423,15 @@
       <c r="I130" s="1">
         <v>1</v>
       </c>
-      <c r="J130" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>6级容器-保险柜</v>
-      </c>
+      <c r="J130" s="2"/>
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="G1:G130" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/data/c_vessel(容器).xlsx
+++ b/data/c_vessel(容器).xlsx
@@ -3654,7 +3654,7 @@
         <v>31</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>33</v>
@@ -3786,7 +3786,7 @@
         <v>31</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>34</v>
@@ -3918,7 +3918,7 @@
         <v>31</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>35</v>
@@ -3929,8 +3929,8 @@
       <c r="F85" s="3">
         <v>30032</v>
       </c>
-      <c r="G85" s="3">
-        <v>0</v>
+      <c r="G85" s="1">
+        <v>5000</v>
       </c>
       <c r="H85" s="3">
         <v>1</v>
@@ -3950,7 +3950,7 @@
       <c r="B86" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3983,7 +3983,7 @@
       <c r="B87" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -4016,7 +4016,7 @@
       <c r="B88" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -4049,8 +4049,8 @@
       <c r="B89" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>22</v>
+      <c r="C89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>36</v>
@@ -4082,7 +4082,7 @@
       <c r="B90" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -4115,7 +4115,7 @@
       <c r="B91" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -4148,7 +4148,7 @@
       <c r="B92" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D92" s="1" t="s">
@@ -4181,8 +4181,8 @@
       <c r="B93" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>22</v>
+      <c r="C93" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>37</v>
@@ -4214,7 +4214,7 @@
       <c r="B94" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -4247,7 +4247,7 @@
       <c r="B95" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -4280,7 +4280,7 @@
       <c r="B96" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -4313,8 +4313,8 @@
       <c r="B97" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>22</v>
+      <c r="C97" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>38</v>
@@ -4346,7 +4346,7 @@
       <c r="B98" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -4446,7 +4446,7 @@
         <v>39</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>41</v>
@@ -4455,10 +4455,10 @@
         <v>4001</v>
       </c>
       <c r="F101" s="1">
-        <v>40013</v>
+        <v>40012</v>
       </c>
       <c r="G101" s="1">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="H101" s="1">
         <v>1</v>
@@ -4479,7 +4479,7 @@
         <v>39</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>41</v>
@@ -4488,10 +4488,10 @@
         <v>4001</v>
       </c>
       <c r="F102" s="1">
-        <v>40012</v>
+        <v>40011</v>
       </c>
       <c r="G102" s="1">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H102" s="1">
         <v>1</v>
@@ -4578,7 +4578,7 @@
         <v>39</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>42</v>
@@ -4587,10 +4587,10 @@
         <v>4002</v>
       </c>
       <c r="F105" s="1">
-        <v>40023</v>
+        <v>40022</v>
       </c>
       <c r="G105" s="1">
-        <v>5000</v>
+        <v>3400</v>
       </c>
       <c r="H105" s="1">
         <v>1</v>
@@ -4611,7 +4611,7 @@
         <v>39</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>42</v>
@@ -4620,10 +4620,10 @@
         <v>4002</v>
       </c>
       <c r="F106" s="1">
-        <v>40022</v>
+        <v>40021</v>
       </c>
       <c r="G106" s="1">
-        <v>3400</v>
+        <v>5000</v>
       </c>
       <c r="H106" s="1">
         <v>1</v>
@@ -4710,7 +4710,7 @@
         <v>39</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>43</v>
@@ -4719,10 +4719,10 @@
         <v>4003</v>
       </c>
       <c r="F109" s="1">
-        <v>40033</v>
+        <v>40032</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="H109" s="1">
         <v>1</v>
@@ -4743,7 +4743,7 @@
         <v>39</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>43</v>
@@ -4752,10 +4752,10 @@
         <v>4003</v>
       </c>
       <c r="F110" s="1">
-        <v>40032</v>
+        <v>40031</v>
       </c>
       <c r="G110" s="1">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H110" s="1">
         <v>1</v>
@@ -4842,7 +4842,7 @@
         <v>39</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>44</v>
@@ -4851,10 +4851,10 @@
         <v>4004</v>
       </c>
       <c r="F113" s="1">
-        <v>40043</v>
+        <v>40042</v>
       </c>
       <c r="G113" s="1">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="H113" s="1">
         <v>1</v>
@@ -4875,7 +4875,7 @@
         <v>39</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>44</v>
@@ -4884,10 +4884,10 @@
         <v>4004</v>
       </c>
       <c r="F114" s="1">
-        <v>40042</v>
+        <v>40041</v>
       </c>
       <c r="G114" s="1">
-        <v>3400</v>
+        <v>5000</v>
       </c>
       <c r="H114" s="1">
         <v>1</v>
@@ -4974,7 +4974,7 @@
         <v>39</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>45</v>
@@ -4983,10 +4983,10 @@
         <v>4005</v>
       </c>
       <c r="F117" s="1">
-        <v>40053</v>
+        <v>40052</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="H117" s="1">
         <v>1</v>
@@ -5007,7 +5007,7 @@
         <v>39</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>45</v>
@@ -5016,10 +5016,10 @@
         <v>4005</v>
       </c>
       <c r="F118" s="1">
-        <v>40052</v>
+        <v>40051</v>
       </c>
       <c r="G118" s="1">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H118" s="1">
         <v>1</v>
@@ -5106,7 +5106,7 @@
         <v>46</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>48</v>
@@ -5115,10 +5115,10 @@
         <v>5001</v>
       </c>
       <c r="F121" s="1">
-        <v>50014</v>
+        <v>50013</v>
       </c>
       <c r="G121" s="1">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="H121" s="1">
         <v>1</v>
@@ -5139,7 +5139,7 @@
         <v>46</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>48</v>
@@ -5148,10 +5148,10 @@
         <v>5001</v>
       </c>
       <c r="F122" s="1">
-        <v>50013</v>
+        <v>50012</v>
       </c>
       <c r="G122" s="1">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H122" s="1">
         <v>1</v>
@@ -5238,7 +5238,7 @@
         <v>46</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>49</v>
@@ -5247,7 +5247,7 @@
         <v>5002</v>
       </c>
       <c r="F125" s="5">
-        <v>50024</v>
+        <v>50023</v>
       </c>
       <c r="G125" s="5">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>46</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>49</v>
@@ -5280,7 +5280,7 @@
         <v>5002</v>
       </c>
       <c r="F126" s="5">
-        <v>50023</v>
+        <v>50022</v>
       </c>
       <c r="G126" s="5">
         <v>0</v>
@@ -5370,7 +5370,7 @@
         <v>50</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>52</v>
@@ -5379,10 +5379,10 @@
         <v>6001</v>
       </c>
       <c r="F129" s="1">
-        <v>60015</v>
+        <v>60014</v>
       </c>
       <c r="G129" s="1">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="H129" s="1">
         <v>1</v>
@@ -5403,7 +5403,7 @@
         <v>50</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>52</v>
@@ -5412,10 +5412,10 @@
         <v>6001</v>
       </c>
       <c r="F130" s="1">
-        <v>60014</v>
+        <v>60013</v>
       </c>
       <c r="G130" s="1">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H130" s="1">
         <v>1</v>

--- a/data/c_vessel(容器).xlsx
+++ b/data/c_vessel(容器).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -818,7 +818,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -827,6 +827,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -889,6 +892,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.799737540818506"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1224,7 +1236,7 @@
       <c r="F3" s="1">
         <v>10011</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="3">
         <v>10000</v>
       </c>
       <c r="H3" s="1">
@@ -1233,8 +1245,9 @@
       <c r="I3" s="1">
         <v>1</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="K3" s="2">
+        <v>10000</v>
+      </c>
       <c r="M3" s="2"/>
     </row>
     <row r="4" ht="14.25" spans="1:13">
@@ -1256,17 +1269,18 @@
       <c r="F4" s="1">
         <v>10011</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
         <v>6600</v>
       </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
@@ -1289,7 +1303,7 @@
       <c r="F5" s="1">
         <v>10011</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="H5" s="1">
@@ -1298,8 +1312,9 @@
       <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
@@ -1322,17 +1337,18 @@
       <c r="F6" s="1">
         <v>10011</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
         <v>3400</v>
       </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
@@ -1355,7 +1371,7 @@
       <c r="F7" s="1">
         <v>10021</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="3">
         <v>10000</v>
       </c>
       <c r="H7" s="1">
@@ -1364,8 +1380,9 @@
       <c r="I7" s="1">
         <v>1</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="K7" s="2">
+        <v>10000</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
@@ -1388,17 +1405,18 @@
       <c r="F8" s="1">
         <v>10021</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
         <v>6600</v>
       </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
@@ -1421,7 +1439,7 @@
       <c r="F9" s="1">
         <v>10021</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" s="1">
@@ -1430,8 +1448,9 @@
       <c r="I9" s="1">
         <v>1</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
@@ -1454,17 +1473,18 @@
       <c r="F10" s="1">
         <v>10021</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
         <v>3400</v>
       </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
@@ -1487,7 +1507,7 @@
       <c r="F11" s="1">
         <v>10031</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="3">
         <v>10000</v>
       </c>
       <c r="H11" s="1">
@@ -1496,8 +1516,9 @@
       <c r="I11" s="1">
         <v>1</v>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="K11" s="2">
+        <v>10000</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
@@ -1520,17 +1541,18 @@
       <c r="F12" s="1">
         <v>10031</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
         <v>6600</v>
       </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
@@ -1553,7 +1575,7 @@
       <c r="F13" s="1">
         <v>10031</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="3">
         <v>0</v>
       </c>
       <c r="H13" s="1">
@@ -1562,8 +1584,9 @@
       <c r="I13" s="1">
         <v>1</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
@@ -1586,17 +1609,18 @@
       <c r="F14" s="1">
         <v>10031</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2">
         <v>3400</v>
       </c>
-      <c r="H14" s="1">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
@@ -1619,7 +1643,7 @@
       <c r="F15" s="1">
         <v>10041</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="3">
         <v>10000</v>
       </c>
       <c r="H15" s="1">
@@ -1628,8 +1652,9 @@
       <c r="I15" s="1">
         <v>1</v>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="K15" s="2">
+        <v>10000</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
     </row>
@@ -1652,17 +1677,18 @@
       <c r="F16" s="1">
         <v>10041</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2">
         <v>6600</v>
       </c>
-      <c r="H16" s="1">
-        <v>1</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
     </row>
@@ -1685,7 +1711,7 @@
       <c r="F17" s="1">
         <v>10041</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="3">
         <v>0</v>
       </c>
       <c r="H17" s="1">
@@ -1694,8 +1720,9 @@
       <c r="I17" s="1">
         <v>1</v>
       </c>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="1"/>
     </row>
@@ -1718,17 +1745,18 @@
       <c r="F18" s="1">
         <v>10041</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2">
         <v>3400</v>
       </c>
-      <c r="H18" s="1">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
     </row>
@@ -1751,7 +1779,7 @@
       <c r="F19" s="1">
         <v>10051</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="3">
         <v>10000</v>
       </c>
       <c r="H19" s="1">
@@ -1760,8 +1788,9 @@
       <c r="I19" s="1">
         <v>1</v>
       </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+      <c r="K19" s="2">
+        <v>10000</v>
+      </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
     </row>
@@ -1784,17 +1813,18 @@
       <c r="F20" s="1">
         <v>10051</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2">
         <v>6600</v>
       </c>
-      <c r="H20" s="1">
-        <v>1</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
     </row>
@@ -1817,7 +1847,7 @@
       <c r="F21" s="1">
         <v>10051</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="3">
         <v>0</v>
       </c>
       <c r="H21" s="1">
@@ -1826,8 +1856,9 @@
       <c r="I21" s="1">
         <v>1</v>
       </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
     </row>
@@ -1850,17 +1881,18 @@
       <c r="F22" s="1">
         <v>10051</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2">
         <v>3400</v>
       </c>
-      <c r="H22" s="1">
-        <v>1</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
     </row>
@@ -1883,7 +1915,7 @@
       <c r="F23" s="1">
         <v>10061</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="3">
         <v>10000</v>
       </c>
       <c r="H23" s="1">
@@ -1892,8 +1924,9 @@
       <c r="I23" s="1">
         <v>1</v>
       </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
+      <c r="K23" s="2">
+        <v>10000</v>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
@@ -1916,17 +1949,18 @@
       <c r="F24" s="1">
         <v>10061</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2">
         <v>6600</v>
       </c>
-      <c r="H24" s="1">
-        <v>1</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
     </row>
@@ -1949,7 +1983,7 @@
       <c r="F25" s="1">
         <v>10061</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="3">
         <v>0</v>
       </c>
       <c r="H25" s="1">
@@ -1958,8 +1992,9 @@
       <c r="I25" s="1">
         <v>1</v>
       </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
+      <c r="K25" s="2">
+        <v>0</v>
+      </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
     </row>
@@ -1982,17 +2017,18 @@
       <c r="F26" s="1">
         <v>10061</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2">
         <v>3400</v>
       </c>
-      <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
     </row>
@@ -2015,7 +2051,7 @@
       <c r="F27" s="1">
         <v>10071</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="3">
         <v>10000</v>
       </c>
       <c r="H27" s="1">
@@ -2024,8 +2060,9 @@
       <c r="I27" s="1">
         <v>1</v>
       </c>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
+      <c r="K27" s="2">
+        <v>10000</v>
+      </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
@@ -2048,17 +2085,18 @@
       <c r="F28" s="1">
         <v>10071</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2">
         <v>6600</v>
       </c>
-      <c r="H28" s="1">
-        <v>1</v>
-      </c>
-      <c r="I28" s="1">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
@@ -2081,7 +2119,7 @@
       <c r="F29" s="1">
         <v>10071</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="1">
@@ -2090,8 +2128,9 @@
       <c r="I29" s="1">
         <v>1</v>
       </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
+      <c r="K29" s="2">
+        <v>0</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
@@ -2114,17 +2153,18 @@
       <c r="F30" s="1">
         <v>10071</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2">
         <v>3400</v>
       </c>
-      <c r="H30" s="1">
-        <v>1</v>
-      </c>
-      <c r="I30" s="1">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
@@ -2147,7 +2187,7 @@
       <c r="F31" s="1">
         <v>10081</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="3">
         <v>10000</v>
       </c>
       <c r="H31" s="1">
@@ -2156,8 +2196,9 @@
       <c r="I31" s="1">
         <v>1</v>
       </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
+      <c r="K31" s="2">
+        <v>10000</v>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
@@ -2180,17 +2221,18 @@
       <c r="F32" s="1">
         <v>10081</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2">
         <v>6600</v>
       </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
@@ -2213,7 +2255,7 @@
       <c r="F33" s="1">
         <v>10081</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" s="3">
         <v>0</v>
       </c>
       <c r="H33" s="1">
@@ -2222,8 +2264,9 @@
       <c r="I33" s="1">
         <v>1</v>
       </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
+      <c r="K33" s="2">
+        <v>0</v>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
@@ -2246,17 +2289,18 @@
       <c r="F34" s="1">
         <v>10081</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="2">
         <v>3400</v>
       </c>
-      <c r="H34" s="1">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
@@ -2279,7 +2323,7 @@
       <c r="F35" s="1">
         <v>10091</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" s="3">
         <v>10000</v>
       </c>
       <c r="H35" s="1">
@@ -2288,8 +2332,9 @@
       <c r="I35" s="1">
         <v>1</v>
       </c>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
+      <c r="K35" s="2">
+        <v>10000</v>
+      </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
@@ -2312,17 +2357,18 @@
       <c r="F36" s="1">
         <v>10091</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36" s="2">
         <v>6600</v>
       </c>
-      <c r="H36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
@@ -2345,7 +2391,7 @@
       <c r="F37" s="1">
         <v>10091</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="3">
         <v>0</v>
       </c>
       <c r="H37" s="1">
@@ -2354,8 +2400,9 @@
       <c r="I37" s="1">
         <v>1</v>
       </c>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
+      <c r="K37" s="2">
+        <v>0</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
@@ -2378,17 +2425,18 @@
       <c r="F38" s="1">
         <v>10091</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2">
         <v>3400</v>
       </c>
-      <c r="H38" s="1">
-        <v>1</v>
-      </c>
-      <c r="I38" s="1">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
@@ -2411,7 +2459,7 @@
       <c r="F39" s="1">
         <v>10101</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" s="3">
         <v>10000</v>
       </c>
       <c r="H39" s="1">
@@ -2420,8 +2468,9 @@
       <c r="I39" s="1">
         <v>1</v>
       </c>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
+      <c r="K39" s="2">
+        <v>10000</v>
+      </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
@@ -2444,17 +2493,18 @@
       <c r="F40" s="1">
         <v>10101</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="2">
         <v>6600</v>
       </c>
-      <c r="H40" s="1">
-        <v>1</v>
-      </c>
-      <c r="I40" s="1">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
@@ -2477,7 +2527,7 @@
       <c r="F41" s="1">
         <v>10101</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" s="3">
         <v>0</v>
       </c>
       <c r="H41" s="1">
@@ -2486,8 +2536,9 @@
       <c r="I41" s="1">
         <v>1</v>
       </c>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
+      <c r="K41" s="2">
+        <v>0</v>
+      </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
@@ -2510,17 +2561,18 @@
       <c r="F42" s="1">
         <v>10101</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="2">
         <v>3400</v>
       </c>
-      <c r="H42" s="1">
-        <v>1</v>
-      </c>
-      <c r="I42" s="1">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
@@ -2543,7 +2595,7 @@
       <c r="F43" s="1">
         <v>20012</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43" s="3">
         <v>10000</v>
       </c>
       <c r="H43" s="1">
@@ -2552,8 +2604,9 @@
       <c r="I43" s="1">
         <v>1</v>
       </c>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
+      <c r="K43" s="2">
+        <v>10000</v>
+      </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
@@ -2576,17 +2629,18 @@
       <c r="F44" s="1">
         <v>20011</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G44" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="2">
         <v>6600</v>
       </c>
-      <c r="H44" s="1">
-        <v>1</v>
-      </c>
-      <c r="I44" s="1">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
     </row>
@@ -2609,7 +2663,7 @@
       <c r="F45" s="1">
         <v>20011</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="1">
@@ -2618,8 +2672,9 @@
       <c r="I45" s="1">
         <v>1</v>
       </c>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
+      <c r="K45" s="2">
+        <v>0</v>
+      </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
     </row>
@@ -2642,17 +2697,18 @@
       <c r="F46" s="1">
         <v>20011</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G46" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="2">
         <v>3400</v>
       </c>
-      <c r="H46" s="1">
-        <v>1</v>
-      </c>
-      <c r="I46" s="1">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
     </row>
@@ -2675,7 +2731,7 @@
       <c r="F47" s="1">
         <v>20022</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G47" s="3">
         <v>10000</v>
       </c>
       <c r="H47" s="1">
@@ -2684,8 +2740,9 @@
       <c r="I47" s="1">
         <v>1</v>
       </c>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
+      <c r="K47" s="2">
+        <v>10000</v>
+      </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
     </row>
@@ -2708,17 +2765,18 @@
       <c r="F48" s="1">
         <v>20021</v>
       </c>
-      <c r="G48" s="1">
+      <c r="G48" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="2">
         <v>6600</v>
       </c>
-      <c r="H48" s="1">
-        <v>1</v>
-      </c>
-      <c r="I48" s="1">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
     </row>
@@ -2741,7 +2799,7 @@
       <c r="F49" s="1">
         <v>20021</v>
       </c>
-      <c r="G49" s="1">
+      <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="1">
@@ -2750,8 +2808,9 @@
       <c r="I49" s="1">
         <v>1</v>
       </c>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
+      <c r="K49" s="2">
+        <v>0</v>
+      </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
     </row>
@@ -2774,17 +2833,18 @@
       <c r="F50" s="1">
         <v>20021</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G50" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="2">
         <v>3400</v>
       </c>
-      <c r="H50" s="1">
-        <v>1</v>
-      </c>
-      <c r="I50" s="1">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
@@ -2807,7 +2867,7 @@
       <c r="F51" s="1">
         <v>20032</v>
       </c>
-      <c r="G51" s="1">
+      <c r="G51" s="3">
         <v>10000</v>
       </c>
       <c r="H51" s="1">
@@ -2816,8 +2876,9 @@
       <c r="I51" s="1">
         <v>1</v>
       </c>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
+      <c r="K51" s="2">
+        <v>10000</v>
+      </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
@@ -2840,17 +2901,18 @@
       <c r="F52" s="1">
         <v>20031</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="2">
         <v>6600</v>
       </c>
-      <c r="H52" s="1">
-        <v>1</v>
-      </c>
-      <c r="I52" s="1">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
@@ -2873,17 +2935,18 @@
       <c r="F53" s="1">
         <v>20031</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="2">
         <v>5000</v>
       </c>
-      <c r="H53" s="1">
-        <v>1</v>
-      </c>
-      <c r="I53" s="1">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
@@ -2906,17 +2969,18 @@
       <c r="F54" s="1">
         <v>20031</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G54" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="2">
         <v>3400</v>
       </c>
-      <c r="H54" s="1">
-        <v>1</v>
-      </c>
-      <c r="I54" s="1">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
@@ -2939,7 +3003,7 @@
       <c r="F55" s="1">
         <v>20042</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G55" s="3">
         <v>10000</v>
       </c>
       <c r="H55" s="1">
@@ -2948,8 +3012,9 @@
       <c r="I55" s="1">
         <v>1</v>
       </c>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
+      <c r="K55" s="2">
+        <v>10000</v>
+      </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
@@ -2972,17 +3037,18 @@
       <c r="F56" s="1">
         <v>20041</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G56" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="2">
         <v>6600</v>
       </c>
-      <c r="H56" s="1">
-        <v>1</v>
-      </c>
-      <c r="I56" s="1">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
@@ -3005,17 +3071,18 @@
       <c r="F57" s="1">
         <v>20041</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="2">
         <v>5000</v>
       </c>
-      <c r="H57" s="1">
-        <v>1</v>
-      </c>
-      <c r="I57" s="1">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
@@ -3038,17 +3105,18 @@
       <c r="F58" s="1">
         <v>20041</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1</v>
+      </c>
+      <c r="I58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="2">
         <v>3400</v>
       </c>
-      <c r="H58" s="1">
-        <v>1</v>
-      </c>
-      <c r="I58" s="1">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
@@ -3071,7 +3139,7 @@
       <c r="F59" s="1">
         <v>20052</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" s="3">
         <v>10000</v>
       </c>
       <c r="H59" s="1">
@@ -3080,8 +3148,9 @@
       <c r="I59" s="1">
         <v>1</v>
       </c>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
+      <c r="K59" s="2">
+        <v>10000</v>
+      </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
@@ -3104,17 +3173,18 @@
       <c r="F60" s="1">
         <v>20051</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H60" s="1">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="2">
         <v>6600</v>
       </c>
-      <c r="H60" s="1">
-        <v>1</v>
-      </c>
-      <c r="I60" s="1">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
@@ -3137,17 +3207,18 @@
       <c r="F61" s="1">
         <v>20051</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>1</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61" s="2">
         <v>5000</v>
       </c>
-      <c r="H61" s="1">
-        <v>1</v>
-      </c>
-      <c r="I61" s="1">
-        <v>1</v>
-      </c>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
     </row>
@@ -3170,17 +3241,18 @@
       <c r="F62" s="1">
         <v>20051</v>
       </c>
-      <c r="G62" s="1">
+      <c r="G62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1</v>
+      </c>
+      <c r="K62" s="2">
         <v>3400</v>
       </c>
-      <c r="H62" s="1">
-        <v>1</v>
-      </c>
-      <c r="I62" s="1">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
     </row>
@@ -3203,7 +3275,7 @@
       <c r="F63" s="1">
         <v>20062</v>
       </c>
-      <c r="G63" s="1">
+      <c r="G63" s="3">
         <v>10000</v>
       </c>
       <c r="H63" s="1">
@@ -3212,8 +3284,9 @@
       <c r="I63" s="1">
         <v>1</v>
       </c>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
+      <c r="K63" s="2">
+        <v>10000</v>
+      </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
     </row>
@@ -3236,17 +3309,18 @@
       <c r="F64" s="1">
         <v>20061</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G64" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1">
+        <v>1</v>
+      </c>
+      <c r="K64" s="2">
         <v>6600</v>
       </c>
-      <c r="H64" s="1">
-        <v>1</v>
-      </c>
-      <c r="I64" s="1">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
     </row>
@@ -3269,17 +3343,18 @@
       <c r="F65" s="1">
         <v>20061</v>
       </c>
-      <c r="G65" s="1">
+      <c r="G65" s="3">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1">
+        <v>1</v>
+      </c>
+      <c r="K65" s="2">
         <v>5000</v>
       </c>
-      <c r="H65" s="1">
-        <v>1</v>
-      </c>
-      <c r="I65" s="1">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
     </row>
@@ -3302,17 +3377,18 @@
       <c r="F66" s="1">
         <v>20061</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="2">
         <v>3400</v>
       </c>
-      <c r="H66" s="1">
-        <v>1</v>
-      </c>
-      <c r="I66" s="1">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
     </row>
@@ -3335,7 +3411,7 @@
       <c r="F67" s="1">
         <v>20072</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G67" s="3">
         <v>10000</v>
       </c>
       <c r="H67" s="1">
@@ -3344,8 +3420,9 @@
       <c r="I67" s="1">
         <v>1</v>
       </c>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
+      <c r="K67" s="2">
+        <v>10000</v>
+      </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
     </row>
@@ -3368,17 +3445,18 @@
       <c r="F68" s="1">
         <v>20071</v>
       </c>
-      <c r="G68" s="1">
+      <c r="G68" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68" s="2">
         <v>6600</v>
       </c>
-      <c r="H68" s="1">
-        <v>1</v>
-      </c>
-      <c r="I68" s="1">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
     </row>
@@ -3401,7 +3479,7 @@
       <c r="F69" s="1">
         <v>20071</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G69" s="3">
         <v>0</v>
       </c>
       <c r="H69" s="1">
@@ -3410,8 +3488,9 @@
       <c r="I69" s="1">
         <v>1</v>
       </c>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
+      <c r="K69" s="2">
+        <v>0</v>
+      </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
     </row>
@@ -3434,17 +3513,18 @@
       <c r="F70" s="1">
         <v>20071</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G70" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1</v>
+      </c>
+      <c r="K70" s="2">
         <v>3400</v>
       </c>
-      <c r="H70" s="1">
-        <v>1</v>
-      </c>
-      <c r="I70" s="1">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
     </row>
@@ -3467,7 +3547,7 @@
       <c r="F71" s="1">
         <v>20082</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G71" s="3">
         <v>10000</v>
       </c>
       <c r="H71" s="1">
@@ -3476,8 +3556,9 @@
       <c r="I71" s="1">
         <v>1</v>
       </c>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
+      <c r="K71" s="2">
+        <v>10000</v>
+      </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
     </row>
@@ -3500,17 +3581,18 @@
       <c r="F72" s="1">
         <v>20081</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G72" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1</v>
+      </c>
+      <c r="I72" s="1">
+        <v>1</v>
+      </c>
+      <c r="K72" s="2">
         <v>6600</v>
       </c>
-      <c r="H72" s="1">
-        <v>1</v>
-      </c>
-      <c r="I72" s="1">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
     </row>
@@ -3533,7 +3615,7 @@
       <c r="F73" s="1">
         <v>20081</v>
       </c>
-      <c r="G73" s="1">
+      <c r="G73" s="3">
         <v>0</v>
       </c>
       <c r="H73" s="1">
@@ -3542,8 +3624,9 @@
       <c r="I73" s="1">
         <v>1</v>
       </c>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
+      <c r="K73" s="2">
+        <v>0</v>
+      </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
     </row>
@@ -3566,17 +3649,18 @@
       <c r="F74" s="1">
         <v>20081</v>
       </c>
-      <c r="G74" s="1">
+      <c r="G74" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H74" s="1">
+        <v>1</v>
+      </c>
+      <c r="I74" s="1">
+        <v>1</v>
+      </c>
+      <c r="K74" s="2">
         <v>3400</v>
       </c>
-      <c r="H74" s="1">
-        <v>1</v>
-      </c>
-      <c r="I74" s="1">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
     </row>
@@ -3599,7 +3683,7 @@
       <c r="F75" s="1">
         <v>30013</v>
       </c>
-      <c r="G75" s="1">
+      <c r="G75" s="3">
         <v>10000</v>
       </c>
       <c r="H75" s="1">
@@ -3608,8 +3692,9 @@
       <c r="I75" s="1">
         <v>1</v>
       </c>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
+      <c r="K75" s="2">
+        <v>10000</v>
+      </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
     </row>
@@ -3632,17 +3717,18 @@
       <c r="F76" s="1">
         <v>30012</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G76" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1</v>
+      </c>
+      <c r="K76" s="2">
         <v>6600</v>
       </c>
-      <c r="H76" s="1">
-        <v>1</v>
-      </c>
-      <c r="I76" s="1">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
     </row>
@@ -3653,29 +3739,30 @@
       <c r="B77" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D77" s="3" t="s">
+      <c r="C77" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E77" s="4">
         <v>3001</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77" s="4">
         <v>30012</v>
       </c>
-      <c r="G77" s="1">
+      <c r="G77" s="3">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4">
+        <v>1</v>
+      </c>
+      <c r="I77" s="4">
+        <v>1</v>
+      </c>
+      <c r="K77" s="5">
         <v>5000</v>
       </c>
-      <c r="H77" s="3">
-        <v>1</v>
-      </c>
-      <c r="I77" s="3">
-        <v>1</v>
-      </c>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
     </row>
@@ -3686,29 +3773,30 @@
       <c r="B78" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D78" s="3" t="s">
+      <c r="C78" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E78" s="3">
+      <c r="E78" s="4">
         <v>3001</v>
       </c>
-      <c r="F78" s="3">
+      <c r="F78" s="4">
         <v>30011</v>
       </c>
       <c r="G78" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H78" s="4">
+        <v>1</v>
+      </c>
+      <c r="I78" s="4">
+        <v>1</v>
+      </c>
+      <c r="K78" s="5">
         <v>3400</v>
       </c>
-      <c r="H78" s="3">
-        <v>1</v>
-      </c>
-      <c r="I78" s="3">
-        <v>1</v>
-      </c>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
     </row>
@@ -3719,29 +3807,30 @@
       <c r="B79" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E79" s="3">
+      <c r="E79" s="4">
         <v>3002</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F79" s="4">
         <v>30023</v>
       </c>
       <c r="G79" s="3">
         <v>10000</v>
       </c>
-      <c r="H79" s="3">
-        <v>1</v>
-      </c>
-      <c r="I79" s="3">
-        <v>1</v>
-      </c>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
+      <c r="H79" s="4">
+        <v>1</v>
+      </c>
+      <c r="I79" s="4">
+        <v>1</v>
+      </c>
+      <c r="K79" s="5">
+        <v>10000</v>
+      </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
     </row>
@@ -3752,29 +3841,30 @@
       <c r="B80" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E80" s="3">
+      <c r="E80" s="4">
         <v>3002</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80" s="4">
         <v>30022</v>
       </c>
       <c r="G80" s="3">
+        <v>0</v>
+      </c>
+      <c r="H80" s="4">
+        <v>1</v>
+      </c>
+      <c r="I80" s="4">
+        <v>1</v>
+      </c>
+      <c r="K80" s="5">
         <v>6600</v>
       </c>
-      <c r="H80" s="3">
-        <v>1</v>
-      </c>
-      <c r="I80" s="3">
-        <v>1</v>
-      </c>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
     </row>
@@ -3785,29 +3875,30 @@
       <c r="B81" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" s="3" t="s">
+      <c r="C81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E81" s="3">
+      <c r="E81" s="4">
         <v>3002</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="4">
         <v>30022</v>
       </c>
       <c r="G81" s="3">
         <v>0</v>
       </c>
-      <c r="H81" s="3">
-        <v>1</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1</v>
-      </c>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
+      <c r="H81" s="4">
+        <v>1</v>
+      </c>
+      <c r="I81" s="4">
+        <v>1</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
     </row>
@@ -3818,29 +3909,30 @@
       <c r="B82" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" s="3" t="s">
+      <c r="C82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E82" s="3">
+      <c r="E82" s="4">
         <v>3002</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F82" s="4">
         <v>30021</v>
       </c>
       <c r="G82" s="3">
+        <v>0</v>
+      </c>
+      <c r="H82" s="4">
+        <v>1</v>
+      </c>
+      <c r="I82" s="4">
+        <v>1</v>
+      </c>
+      <c r="K82" s="5">
         <v>3400</v>
       </c>
-      <c r="H82" s="3">
-        <v>1</v>
-      </c>
-      <c r="I82" s="3">
-        <v>1</v>
-      </c>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
     </row>
@@ -3851,29 +3943,30 @@
       <c r="B83" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="4">
         <v>3003</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="4">
         <v>30033</v>
       </c>
       <c r="G83" s="3">
         <v>10000</v>
       </c>
-      <c r="H83" s="3">
-        <v>1</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1</v>
-      </c>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
+      <c r="H83" s="4">
+        <v>1</v>
+      </c>
+      <c r="I83" s="4">
+        <v>1</v>
+      </c>
+      <c r="K83" s="5">
+        <v>10000</v>
+      </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
     </row>
@@ -3884,29 +3977,30 @@
       <c r="B84" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="3">
+      <c r="E84" s="4">
         <v>3003</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84" s="4">
         <v>30032</v>
       </c>
       <c r="G84" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H84" s="4">
+        <v>1</v>
+      </c>
+      <c r="I84" s="4">
+        <v>1</v>
+      </c>
+      <c r="K84" s="5">
         <v>6600</v>
       </c>
-      <c r="H84" s="3">
-        <v>1</v>
-      </c>
-      <c r="I84" s="3">
-        <v>1</v>
-      </c>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
     </row>
@@ -3917,29 +4011,30 @@
       <c r="B85" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D85" s="3" t="s">
+      <c r="C85" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E85" s="3">
+      <c r="E85" s="4">
         <v>3003</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85" s="4">
         <v>30032</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G85" s="3">
+        <v>0</v>
+      </c>
+      <c r="H85" s="4">
+        <v>1</v>
+      </c>
+      <c r="I85" s="4">
+        <v>1</v>
+      </c>
+      <c r="K85" s="5">
         <v>5000</v>
       </c>
-      <c r="H85" s="3">
-        <v>1</v>
-      </c>
-      <c r="I85" s="3">
-        <v>1</v>
-      </c>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
     </row>
@@ -3950,7 +4045,7 @@
       <c r="B86" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3962,17 +4057,18 @@
       <c r="F86" s="1">
         <v>30031</v>
       </c>
-      <c r="G86" s="1">
+      <c r="G86" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H86" s="1">
+        <v>1</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1</v>
+      </c>
+      <c r="K86" s="2">
         <v>3400</v>
       </c>
-      <c r="H86" s="1">
-        <v>1</v>
-      </c>
-      <c r="I86" s="1">
-        <v>1</v>
-      </c>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
     </row>
@@ -3983,7 +4079,7 @@
       <c r="B87" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -3995,7 +4091,7 @@
       <c r="F87" s="1">
         <v>30043</v>
       </c>
-      <c r="G87" s="1">
+      <c r="G87" s="3">
         <v>10000</v>
       </c>
       <c r="H87" s="1">
@@ -4004,8 +4100,9 @@
       <c r="I87" s="1">
         <v>1</v>
       </c>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
+      <c r="K87" s="2">
+        <v>10000</v>
+      </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
     </row>
@@ -4016,7 +4113,7 @@
       <c r="B88" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -4028,17 +4125,18 @@
       <c r="F88" s="1">
         <v>30042</v>
       </c>
-      <c r="G88" s="1">
+      <c r="G88" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H88" s="1">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1">
+        <v>1</v>
+      </c>
+      <c r="K88" s="2">
         <v>6600</v>
       </c>
-      <c r="H88" s="1">
-        <v>1</v>
-      </c>
-      <c r="I88" s="1">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
     </row>
@@ -4049,7 +4147,7 @@
       <c r="B89" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -4061,7 +4159,7 @@
       <c r="F89" s="1">
         <v>30042</v>
       </c>
-      <c r="G89" s="1">
+      <c r="G89" s="3">
         <v>0</v>
       </c>
       <c r="H89" s="1">
@@ -4070,8 +4168,9 @@
       <c r="I89" s="1">
         <v>1</v>
       </c>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
+      <c r="K89" s="2">
+        <v>0</v>
+      </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
     </row>
@@ -4082,7 +4181,7 @@
       <c r="B90" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -4094,17 +4193,18 @@
       <c r="F90" s="1">
         <v>30041</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G90" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H90" s="1">
+        <v>1</v>
+      </c>
+      <c r="I90" s="1">
+        <v>1</v>
+      </c>
+      <c r="K90" s="2">
         <v>3400</v>
       </c>
-      <c r="H90" s="1">
-        <v>1</v>
-      </c>
-      <c r="I90" s="1">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
     </row>
@@ -4115,7 +4215,7 @@
       <c r="B91" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -4127,7 +4227,7 @@
       <c r="F91" s="1">
         <v>30053</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G91" s="3">
         <v>10000</v>
       </c>
       <c r="H91" s="1">
@@ -4136,8 +4236,9 @@
       <c r="I91" s="1">
         <v>1</v>
       </c>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
+      <c r="K91" s="2">
+        <v>10000</v>
+      </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
     </row>
@@ -4148,7 +4249,7 @@
       <c r="B92" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D92" s="1" t="s">
@@ -4160,17 +4261,18 @@
       <c r="F92" s="1">
         <v>30052</v>
       </c>
-      <c r="G92" s="1">
+      <c r="G92" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H92" s="1">
+        <v>1</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1</v>
+      </c>
+      <c r="K92" s="2">
         <v>6600</v>
       </c>
-      <c r="H92" s="1">
-        <v>1</v>
-      </c>
-      <c r="I92" s="1">
-        <v>1</v>
-      </c>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
     </row>
@@ -4181,7 +4283,7 @@
       <c r="B93" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -4193,17 +4295,18 @@
       <c r="F93" s="1">
         <v>30052</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G93" s="3">
+        <v>0</v>
+      </c>
+      <c r="H93" s="1">
+        <v>1</v>
+      </c>
+      <c r="I93" s="1">
+        <v>1</v>
+      </c>
+      <c r="K93" s="2">
         <v>5000</v>
       </c>
-      <c r="H93" s="1">
-        <v>1</v>
-      </c>
-      <c r="I93" s="1">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
     </row>
@@ -4214,7 +4317,7 @@
       <c r="B94" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -4226,17 +4329,18 @@
       <c r="F94" s="1">
         <v>30051</v>
       </c>
-      <c r="G94" s="1">
+      <c r="G94" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H94" s="1">
+        <v>1</v>
+      </c>
+      <c r="I94" s="1">
+        <v>1</v>
+      </c>
+      <c r="K94" s="2">
         <v>3400</v>
       </c>
-      <c r="H94" s="1">
-        <v>1</v>
-      </c>
-      <c r="I94" s="1">
-        <v>1</v>
-      </c>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
     </row>
@@ -4247,7 +4351,7 @@
       <c r="B95" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -4259,7 +4363,7 @@
       <c r="F95" s="1">
         <v>30063</v>
       </c>
-      <c r="G95" s="1">
+      <c r="G95" s="3">
         <v>10000</v>
       </c>
       <c r="H95" s="1">
@@ -4268,8 +4372,9 @@
       <c r="I95" s="1">
         <v>1</v>
       </c>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
+      <c r="K95" s="2">
+        <v>10000</v>
+      </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
     </row>
@@ -4280,7 +4385,7 @@
       <c r="B96" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -4292,17 +4397,18 @@
       <c r="F96" s="1">
         <v>30062</v>
       </c>
-      <c r="G96" s="1">
+      <c r="G96" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H96" s="1">
+        <v>1</v>
+      </c>
+      <c r="I96" s="1">
+        <v>1</v>
+      </c>
+      <c r="K96" s="2">
         <v>6600</v>
       </c>
-      <c r="H96" s="1">
-        <v>1</v>
-      </c>
-      <c r="I96" s="1">
-        <v>1</v>
-      </c>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
     </row>
@@ -4313,7 +4419,7 @@
       <c r="B97" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -4325,7 +4431,7 @@
       <c r="F97" s="1">
         <v>30062</v>
       </c>
-      <c r="G97" s="1">
+      <c r="G97" s="3">
         <v>0</v>
       </c>
       <c r="H97" s="1">
@@ -4334,8 +4440,9 @@
       <c r="I97" s="1">
         <v>1</v>
       </c>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
+      <c r="K97" s="2">
+        <v>0</v>
+      </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
     </row>
@@ -4346,7 +4453,7 @@
       <c r="B98" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -4358,17 +4465,18 @@
       <c r="F98" s="1">
         <v>30061</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G98" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H98" s="1">
+        <v>1</v>
+      </c>
+      <c r="I98" s="1">
+        <v>1</v>
+      </c>
+      <c r="K98" s="2">
         <v>3400</v>
       </c>
-      <c r="H98" s="1">
-        <v>1</v>
-      </c>
-      <c r="I98" s="1">
-        <v>1</v>
-      </c>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
     </row>
@@ -4391,7 +4499,7 @@
       <c r="F99" s="1">
         <v>40014</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G99" s="3">
         <v>10000</v>
       </c>
       <c r="H99" s="1">
@@ -4400,8 +4508,9 @@
       <c r="I99" s="1">
         <v>1</v>
       </c>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
+      <c r="K99" s="2">
+        <v>10000</v>
+      </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
     </row>
@@ -4424,17 +4533,18 @@
       <c r="F100" s="1">
         <v>40013</v>
       </c>
-      <c r="G100" s="1">
+      <c r="G100" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H100" s="1">
+        <v>1</v>
+      </c>
+      <c r="I100" s="1">
+        <v>1</v>
+      </c>
+      <c r="K100" s="2">
         <v>6600</v>
       </c>
-      <c r="H100" s="1">
-        <v>1</v>
-      </c>
-      <c r="I100" s="1">
-        <v>1</v>
-      </c>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
     </row>
@@ -4457,17 +4567,18 @@
       <c r="F101" s="1">
         <v>40012</v>
       </c>
-      <c r="G101" s="1">
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="1">
+        <v>1</v>
+      </c>
+      <c r="I101" s="1">
+        <v>1</v>
+      </c>
+      <c r="K101" s="2">
         <v>3400</v>
       </c>
-      <c r="H101" s="1">
-        <v>1</v>
-      </c>
-      <c r="I101" s="1">
-        <v>1</v>
-      </c>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
     </row>
@@ -4490,8 +4601,8 @@
       <c r="F102" s="1">
         <v>40011</v>
       </c>
-      <c r="G102" s="1">
-        <v>0</v>
+      <c r="G102" s="3">
+        <v>2500</v>
       </c>
       <c r="H102" s="1">
         <v>1</v>
@@ -4499,8 +4610,9 @@
       <c r="I102" s="1">
         <v>1</v>
       </c>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
+      <c r="K102" s="2">
+        <v>0</v>
+      </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
     </row>
@@ -4523,7 +4635,7 @@
       <c r="F103" s="1">
         <v>40024</v>
       </c>
-      <c r="G103" s="1">
+      <c r="G103" s="3">
         <v>10000</v>
       </c>
       <c r="H103" s="1">
@@ -4532,8 +4644,9 @@
       <c r="I103" s="1">
         <v>1</v>
       </c>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
+      <c r="K103" s="2">
+        <v>10000</v>
+      </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
     </row>
@@ -4556,17 +4669,18 @@
       <c r="F104" s="1">
         <v>40023</v>
       </c>
-      <c r="G104" s="1">
+      <c r="G104" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H104" s="1">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1">
+        <v>1</v>
+      </c>
+      <c r="K104" s="2">
         <v>6600</v>
       </c>
-      <c r="H104" s="1">
-        <v>1</v>
-      </c>
-      <c r="I104" s="1">
-        <v>1</v>
-      </c>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
     </row>
@@ -4589,17 +4703,18 @@
       <c r="F105" s="1">
         <v>40022</v>
       </c>
-      <c r="G105" s="1">
+      <c r="G105" s="3">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1">
+        <v>1</v>
+      </c>
+      <c r="I105" s="1">
+        <v>1</v>
+      </c>
+      <c r="K105" s="2">
         <v>3400</v>
       </c>
-      <c r="H105" s="1">
-        <v>1</v>
-      </c>
-      <c r="I105" s="1">
-        <v>1</v>
-      </c>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
     </row>
@@ -4622,17 +4737,18 @@
       <c r="F106" s="1">
         <v>40021</v>
       </c>
-      <c r="G106" s="1">
+      <c r="G106" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H106" s="1">
+        <v>1</v>
+      </c>
+      <c r="I106" s="1">
+        <v>1</v>
+      </c>
+      <c r="K106" s="2">
         <v>5000</v>
       </c>
-      <c r="H106" s="1">
-        <v>1</v>
-      </c>
-      <c r="I106" s="1">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
     </row>
@@ -4655,7 +4771,7 @@
       <c r="F107" s="1">
         <v>40034</v>
       </c>
-      <c r="G107" s="1">
+      <c r="G107" s="3">
         <v>10000</v>
       </c>
       <c r="H107" s="1">
@@ -4664,8 +4780,9 @@
       <c r="I107" s="1">
         <v>1</v>
       </c>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
+      <c r="K107" s="2">
+        <v>10000</v>
+      </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
     </row>
@@ -4688,17 +4805,18 @@
       <c r="F108" s="1">
         <v>40033</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G108" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H108" s="1">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1">
+        <v>1</v>
+      </c>
+      <c r="K108" s="2">
         <v>6600</v>
       </c>
-      <c r="H108" s="1">
-        <v>1</v>
-      </c>
-      <c r="I108" s="1">
-        <v>1</v>
-      </c>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
     </row>
@@ -4721,17 +4839,18 @@
       <c r="F109" s="1">
         <v>40032</v>
       </c>
-      <c r="G109" s="1">
+      <c r="G109" s="3">
+        <v>0</v>
+      </c>
+      <c r="H109" s="1">
+        <v>1</v>
+      </c>
+      <c r="I109" s="1">
+        <v>1</v>
+      </c>
+      <c r="K109" s="2">
         <v>3400</v>
       </c>
-      <c r="H109" s="1">
-        <v>1</v>
-      </c>
-      <c r="I109" s="1">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2"/>
-      <c r="K109" s="2"/>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
     </row>
@@ -4754,8 +4873,8 @@
       <c r="F110" s="1">
         <v>40031</v>
       </c>
-      <c r="G110" s="1">
-        <v>0</v>
+      <c r="G110" s="3">
+        <v>2500</v>
       </c>
       <c r="H110" s="1">
         <v>1</v>
@@ -4763,8 +4882,9 @@
       <c r="I110" s="1">
         <v>1</v>
       </c>
-      <c r="J110" s="2"/>
-      <c r="K110" s="2"/>
+      <c r="K110" s="2">
+        <v>0</v>
+      </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
     </row>
@@ -4787,7 +4907,7 @@
       <c r="F111" s="1">
         <v>40044</v>
       </c>
-      <c r="G111" s="1">
+      <c r="G111" s="3">
         <v>10000</v>
       </c>
       <c r="H111" s="1">
@@ -4796,8 +4916,9 @@
       <c r="I111" s="1">
         <v>1</v>
       </c>
-      <c r="J111" s="2"/>
-      <c r="K111" s="2"/>
+      <c r="K111" s="2">
+        <v>10000</v>
+      </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
     </row>
@@ -4820,17 +4941,18 @@
       <c r="F112" s="1">
         <v>40043</v>
       </c>
-      <c r="G112" s="1">
+      <c r="G112" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H112" s="1">
+        <v>1</v>
+      </c>
+      <c r="I112" s="1">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2">
         <v>6600</v>
       </c>
-      <c r="H112" s="1">
-        <v>1</v>
-      </c>
-      <c r="I112" s="1">
-        <v>1</v>
-      </c>
-      <c r="J112" s="2"/>
-      <c r="K112" s="2"/>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
     </row>
@@ -4853,17 +4975,18 @@
       <c r="F113" s="1">
         <v>40042</v>
       </c>
-      <c r="G113" s="1">
+      <c r="G113" s="3">
+        <v>0</v>
+      </c>
+      <c r="H113" s="1">
+        <v>1</v>
+      </c>
+      <c r="I113" s="1">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2">
         <v>3400</v>
       </c>
-      <c r="H113" s="1">
-        <v>1</v>
-      </c>
-      <c r="I113" s="1">
-        <v>1</v>
-      </c>
-      <c r="J113" s="2"/>
-      <c r="K113" s="2"/>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
     </row>
@@ -4886,17 +5009,18 @@
       <c r="F114" s="1">
         <v>40041</v>
       </c>
-      <c r="G114" s="1">
+      <c r="G114" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H114" s="1">
+        <v>1</v>
+      </c>
+      <c r="I114" s="1">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
         <v>5000</v>
       </c>
-      <c r="H114" s="1">
-        <v>1</v>
-      </c>
-      <c r="I114" s="1">
-        <v>1</v>
-      </c>
-      <c r="J114" s="2"/>
-      <c r="K114" s="2"/>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
     </row>
@@ -4919,7 +5043,7 @@
       <c r="F115" s="1">
         <v>40054</v>
       </c>
-      <c r="G115" s="1">
+      <c r="G115" s="3">
         <v>10000</v>
       </c>
       <c r="H115" s="1">
@@ -4928,8 +5052,9 @@
       <c r="I115" s="1">
         <v>1</v>
       </c>
-      <c r="J115" s="2"/>
-      <c r="K115" s="2"/>
+      <c r="K115" s="2">
+        <v>10000</v>
+      </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
     </row>
@@ -4952,17 +5077,18 @@
       <c r="F116" s="1">
         <v>40053</v>
       </c>
-      <c r="G116" s="1">
+      <c r="G116" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H116" s="1">
+        <v>1</v>
+      </c>
+      <c r="I116" s="1">
+        <v>1</v>
+      </c>
+      <c r="K116" s="2">
         <v>6600</v>
       </c>
-      <c r="H116" s="1">
-        <v>1</v>
-      </c>
-      <c r="I116" s="1">
-        <v>1</v>
-      </c>
-      <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
     </row>
@@ -4985,17 +5111,18 @@
       <c r="F117" s="1">
         <v>40052</v>
       </c>
-      <c r="G117" s="1">
+      <c r="G117" s="3">
+        <v>0</v>
+      </c>
+      <c r="H117" s="1">
+        <v>1</v>
+      </c>
+      <c r="I117" s="1">
+        <v>1</v>
+      </c>
+      <c r="K117" s="2">
         <v>3400</v>
       </c>
-      <c r="H117" s="1">
-        <v>1</v>
-      </c>
-      <c r="I117" s="1">
-        <v>1</v>
-      </c>
-      <c r="J117" s="2"/>
-      <c r="K117" s="2"/>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
     </row>
@@ -5018,8 +5145,8 @@
       <c r="F118" s="1">
         <v>40051</v>
       </c>
-      <c r="G118" s="1">
-        <v>0</v>
+      <c r="G118" s="3">
+        <v>2500</v>
       </c>
       <c r="H118" s="1">
         <v>1</v>
@@ -5027,8 +5154,9 @@
       <c r="I118" s="1">
         <v>1</v>
       </c>
-      <c r="J118" s="2"/>
-      <c r="K118" s="2"/>
+      <c r="K118" s="2">
+        <v>0</v>
+      </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
     </row>
@@ -5051,7 +5179,7 @@
       <c r="F119" s="1">
         <v>50015</v>
       </c>
-      <c r="G119" s="1">
+      <c r="G119" s="3">
         <v>10000</v>
       </c>
       <c r="H119" s="1">
@@ -5060,8 +5188,9 @@
       <c r="I119" s="1">
         <v>1</v>
       </c>
-      <c r="J119" s="2"/>
-      <c r="K119" s="2"/>
+      <c r="K119" s="2">
+        <v>10000</v>
+      </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
     </row>
@@ -5084,17 +5213,18 @@
       <c r="F120" s="1">
         <v>50014</v>
       </c>
-      <c r="G120" s="1">
+      <c r="G120" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H120" s="1">
+        <v>1</v>
+      </c>
+      <c r="I120" s="1">
+        <v>1</v>
+      </c>
+      <c r="K120" s="2">
         <v>6600</v>
       </c>
-      <c r="H120" s="1">
-        <v>1</v>
-      </c>
-      <c r="I120" s="1">
-        <v>1</v>
-      </c>
-      <c r="J120" s="2"/>
-      <c r="K120" s="2"/>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
     </row>
@@ -5117,17 +5247,18 @@
       <c r="F121" s="1">
         <v>50013</v>
       </c>
-      <c r="G121" s="1">
+      <c r="G121" s="3">
+        <v>0</v>
+      </c>
+      <c r="H121" s="1">
+        <v>1</v>
+      </c>
+      <c r="I121" s="1">
+        <v>1</v>
+      </c>
+      <c r="K121" s="2">
         <v>3400</v>
       </c>
-      <c r="H121" s="1">
-        <v>1</v>
-      </c>
-      <c r="I121" s="1">
-        <v>1</v>
-      </c>
-      <c r="J121" s="2"/>
-      <c r="K121" s="2"/>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
     </row>
@@ -5150,8 +5281,8 @@
       <c r="F122" s="1">
         <v>50012</v>
       </c>
-      <c r="G122" s="1">
-        <v>0</v>
+      <c r="G122" s="3">
+        <v>2500</v>
       </c>
       <c r="H122" s="1">
         <v>1</v>
@@ -5159,8 +5290,9 @@
       <c r="I122" s="1">
         <v>1</v>
       </c>
-      <c r="J122" s="2"/>
-      <c r="K122" s="2"/>
+      <c r="K122" s="2">
+        <v>0</v>
+      </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
     </row>
@@ -5174,16 +5306,16 @@
       <c r="C123" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D123" s="5" t="s">
+      <c r="D123" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E123" s="5">
+      <c r="E123" s="6">
         <v>5002</v>
       </c>
-      <c r="F123" s="5">
+      <c r="F123" s="6">
         <v>50025</v>
       </c>
-      <c r="G123" s="5">
+      <c r="G123" s="3">
         <v>10000</v>
       </c>
       <c r="H123" s="1">
@@ -5192,8 +5324,9 @@
       <c r="I123" s="1">
         <v>1</v>
       </c>
-      <c r="J123" s="2"/>
-      <c r="K123" s="2"/>
+      <c r="K123" s="2">
+        <v>10000</v>
+      </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
     </row>
@@ -5207,17 +5340,17 @@
       <c r="C124" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D124" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E124" s="5">
+      <c r="E124" s="6">
         <v>5002</v>
       </c>
-      <c r="F124" s="5">
+      <c r="F124" s="6">
         <v>50024</v>
       </c>
-      <c r="G124" s="5">
-        <v>0</v>
+      <c r="G124" s="3">
+        <v>5000</v>
       </c>
       <c r="H124" s="1">
         <v>1</v>
@@ -5225,8 +5358,9 @@
       <c r="I124" s="1">
         <v>1</v>
       </c>
-      <c r="J124" s="2"/>
-      <c r="K124" s="2"/>
+      <c r="K124" s="2">
+        <v>0</v>
+      </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
     </row>
@@ -5240,16 +5374,16 @@
       <c r="C125" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D125" s="5" t="s">
+      <c r="D125" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E125" s="5">
+      <c r="E125" s="6">
         <v>5002</v>
       </c>
-      <c r="F125" s="5">
+      <c r="F125" s="6">
         <v>50023</v>
       </c>
-      <c r="G125" s="5">
+      <c r="G125" s="3">
         <v>0</v>
       </c>
       <c r="H125" s="1">
@@ -5258,8 +5392,9 @@
       <c r="I125" s="1">
         <v>1</v>
       </c>
-      <c r="J125" s="2"/>
-      <c r="K125" s="2"/>
+      <c r="K125" s="2">
+        <v>0</v>
+      </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
     </row>
@@ -5273,17 +5408,17 @@
       <c r="C126" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D126" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E126" s="5">
+      <c r="E126" s="6">
         <v>5002</v>
       </c>
-      <c r="F126" s="5">
+      <c r="F126" s="6">
         <v>50022</v>
       </c>
-      <c r="G126" s="5">
-        <v>0</v>
+      <c r="G126" s="3">
+        <v>2500</v>
       </c>
       <c r="H126" s="1">
         <v>1</v>
@@ -5291,8 +5426,9 @@
       <c r="I126" s="1">
         <v>1</v>
       </c>
-      <c r="J126" s="2"/>
-      <c r="K126" s="2"/>
+      <c r="K126" s="2">
+        <v>0</v>
+      </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
     </row>
@@ -5315,7 +5451,7 @@
       <c r="F127" s="1">
         <v>60016</v>
       </c>
-      <c r="G127" s="1">
+      <c r="G127" s="3">
         <v>10000</v>
       </c>
       <c r="H127" s="1">
@@ -5324,8 +5460,9 @@
       <c r="I127" s="1">
         <v>1</v>
       </c>
-      <c r="J127" s="2"/>
-      <c r="K127" s="2"/>
+      <c r="K127" s="2">
+        <v>10000</v>
+      </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
     </row>
@@ -5348,17 +5485,18 @@
       <c r="F128" s="1">
         <v>60015</v>
       </c>
-      <c r="G128" s="1">
+      <c r="G128" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H128" s="1">
+        <v>1</v>
+      </c>
+      <c r="I128" s="1">
+        <v>1</v>
+      </c>
+      <c r="K128" s="2">
         <v>6600</v>
       </c>
-      <c r="H128" s="1">
-        <v>1</v>
-      </c>
-      <c r="I128" s="1">
-        <v>1</v>
-      </c>
-      <c r="J128" s="2"/>
-      <c r="K128" s="2"/>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
     </row>
@@ -5381,17 +5519,18 @@
       <c r="F129" s="1">
         <v>60014</v>
       </c>
-      <c r="G129" s="1">
+      <c r="G129" s="3">
+        <v>0</v>
+      </c>
+      <c r="H129" s="1">
+        <v>1</v>
+      </c>
+      <c r="I129" s="1">
+        <v>1</v>
+      </c>
+      <c r="K129" s="2">
         <v>3400</v>
       </c>
-      <c r="H129" s="1">
-        <v>1</v>
-      </c>
-      <c r="I129" s="1">
-        <v>1</v>
-      </c>
-      <c r="J129" s="2"/>
-      <c r="K129" s="2"/>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
     </row>
@@ -5414,8 +5553,8 @@
       <c r="F130" s="1">
         <v>60013</v>
       </c>
-      <c r="G130" s="1">
-        <v>0</v>
+      <c r="G130" s="3">
+        <v>2500</v>
       </c>
       <c r="H130" s="1">
         <v>1</v>
@@ -5423,8 +5562,9 @@
       <c r="I130" s="1">
         <v>1</v>
       </c>
-      <c r="J130" s="2"/>
-      <c r="K130" s="2"/>
+      <c r="K130" s="2">
+        <v>0</v>
+      </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
     </row>
@@ -5432,6 +5572,11 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="G1:G130" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
+  <conditionalFormatting sqref="G3:G114">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($D3,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/data/c_vessel(容器).xlsx
+++ b/data/c_vessel(容器).xlsx
@@ -1236,7 +1236,7 @@
       <c r="F3" s="1">
         <v>10011</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>10000</v>
       </c>
       <c r="H3" s="1">
@@ -1245,7 +1245,7 @@
       <c r="I3" s="1">
         <v>1</v>
       </c>
-      <c r="K3" s="2">
+      <c r="J3" s="3">
         <v>10000</v>
       </c>
       <c r="M3" s="2"/>
@@ -1269,17 +1269,17 @@
       <c r="F4" s="1">
         <v>10011</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
         <v>5000</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2">
-        <v>6600</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1303,7 +1303,7 @@
       <c r="F5" s="1">
         <v>10011</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="1">
@@ -1312,7 +1312,7 @@
       <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="2">
+      <c r="J5" s="3">
         <v>0</v>
       </c>
       <c r="L5" s="2"/>
@@ -1337,17 +1337,17 @@
       <c r="F6" s="1">
         <v>10011</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3">
         <v>2500</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2">
-        <v>3400</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -1371,7 +1371,7 @@
       <c r="F7" s="1">
         <v>10021</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>10000</v>
       </c>
       <c r="H7" s="1">
@@ -1380,7 +1380,7 @@
       <c r="I7" s="1">
         <v>1</v>
       </c>
-      <c r="K7" s="2">
+      <c r="J7" s="3">
         <v>10000</v>
       </c>
       <c r="L7" s="2"/>
@@ -1405,17 +1405,17 @@
       <c r="F8" s="1">
         <v>10021</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3">
         <v>5000</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2">
-        <v>6600</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1439,7 +1439,7 @@
       <c r="F9" s="1">
         <v>10021</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="1">
@@ -1448,7 +1448,7 @@
       <c r="I9" s="1">
         <v>1</v>
       </c>
-      <c r="K9" s="2">
+      <c r="J9" s="3">
         <v>0</v>
       </c>
       <c r="L9" s="2"/>
@@ -1473,17 +1473,17 @@
       <c r="F10" s="1">
         <v>10021</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
         <v>2500</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2">
-        <v>3400</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -1507,7 +1507,7 @@
       <c r="F11" s="1">
         <v>10031</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>10000</v>
       </c>
       <c r="H11" s="1">
@@ -1516,7 +1516,7 @@
       <c r="I11" s="1">
         <v>1</v>
       </c>
-      <c r="K11" s="2">
+      <c r="J11" s="3">
         <v>10000</v>
       </c>
       <c r="L11" s="2"/>
@@ -1541,17 +1541,17 @@
       <c r="F12" s="1">
         <v>10031</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
         <v>5000</v>
-      </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2">
-        <v>6600</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1575,7 +1575,7 @@
       <c r="F13" s="1">
         <v>10031</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="1">
@@ -1584,7 +1584,7 @@
       <c r="I13" s="1">
         <v>1</v>
       </c>
-      <c r="K13" s="2">
+      <c r="J13" s="3">
         <v>0</v>
       </c>
       <c r="L13" s="2"/>
@@ -1609,17 +1609,17 @@
       <c r="F14" s="1">
         <v>10031</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3">
         <v>2500</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2">
-        <v>3400</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -1643,7 +1643,7 @@
       <c r="F15" s="1">
         <v>10041</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>10000</v>
       </c>
       <c r="H15" s="1">
@@ -1652,7 +1652,7 @@
       <c r="I15" s="1">
         <v>1</v>
       </c>
-      <c r="K15" s="2">
+      <c r="J15" s="3">
         <v>10000</v>
       </c>
       <c r="L15" s="2"/>
@@ -1677,17 +1677,17 @@
       <c r="F16" s="1">
         <v>10041</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3">
         <v>5000</v>
-      </c>
-      <c r="H16" s="1">
-        <v>1</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2">
-        <v>6600</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1711,7 +1711,7 @@
       <c r="F17" s="1">
         <v>10041</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="1">
@@ -1720,7 +1720,7 @@
       <c r="I17" s="1">
         <v>1</v>
       </c>
-      <c r="K17" s="2">
+      <c r="J17" s="3">
         <v>0</v>
       </c>
       <c r="L17" s="2"/>
@@ -1745,17 +1745,17 @@
       <c r="F18" s="1">
         <v>10041</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3">
         <v>2500</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="2">
-        <v>3400</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1779,7 +1779,7 @@
       <c r="F19" s="1">
         <v>10051</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <v>10000</v>
       </c>
       <c r="H19" s="1">
@@ -1788,7 +1788,7 @@
       <c r="I19" s="1">
         <v>1</v>
       </c>
-      <c r="K19" s="2">
+      <c r="J19" s="3">
         <v>10000</v>
       </c>
       <c r="L19" s="2"/>
@@ -1813,17 +1813,17 @@
       <c r="F20" s="1">
         <v>10051</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3">
         <v>5000</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2">
-        <v>6600</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -1847,7 +1847,7 @@
       <c r="F21" s="1">
         <v>10051</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="1">
@@ -1856,7 +1856,7 @@
       <c r="I21" s="1">
         <v>1</v>
       </c>
-      <c r="K21" s="2">
+      <c r="J21" s="3">
         <v>0</v>
       </c>
       <c r="L21" s="2"/>
@@ -1881,17 +1881,17 @@
       <c r="F22" s="1">
         <v>10051</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3">
         <v>2500</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2">
-        <v>3400</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1915,7 +1915,7 @@
       <c r="F23" s="1">
         <v>10061</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="2">
         <v>10000</v>
       </c>
       <c r="H23" s="1">
@@ -1924,7 +1924,7 @@
       <c r="I23" s="1">
         <v>1</v>
       </c>
-      <c r="K23" s="2">
+      <c r="J23" s="3">
         <v>10000</v>
       </c>
       <c r="L23" s="2"/>
@@ -1949,17 +1949,17 @@
       <c r="F24" s="1">
         <v>10061</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="3">
         <v>5000</v>
-      </c>
-      <c r="H24" s="1">
-        <v>1</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="2">
-        <v>6600</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -1983,7 +1983,7 @@
       <c r="F25" s="1">
         <v>10061</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="1">
@@ -1992,7 +1992,7 @@
       <c r="I25" s="1">
         <v>1</v>
       </c>
-      <c r="K25" s="2">
+      <c r="J25" s="3">
         <v>0</v>
       </c>
       <c r="L25" s="2"/>
@@ -2017,17 +2017,17 @@
       <c r="F26" s="1">
         <v>10061</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3">
         <v>2500</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="2">
-        <v>3400</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2051,7 +2051,7 @@
       <c r="F27" s="1">
         <v>10071</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="2">
         <v>10000</v>
       </c>
       <c r="H27" s="1">
@@ -2060,7 +2060,7 @@
       <c r="I27" s="1">
         <v>1</v>
       </c>
-      <c r="K27" s="2">
+      <c r="J27" s="3">
         <v>10000</v>
       </c>
       <c r="L27" s="2"/>
@@ -2085,17 +2085,17 @@
       <c r="F28" s="1">
         <v>10071</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3">
         <v>5000</v>
-      </c>
-      <c r="H28" s="1">
-        <v>1</v>
-      </c>
-      <c r="I28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="2">
-        <v>6600</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -2119,7 +2119,7 @@
       <c r="F29" s="1">
         <v>10071</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="1">
@@ -2128,7 +2128,7 @@
       <c r="I29" s="1">
         <v>1</v>
       </c>
-      <c r="K29" s="2">
+      <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="L29" s="2"/>
@@ -2153,17 +2153,17 @@
       <c r="F30" s="1">
         <v>10071</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3">
         <v>2500</v>
-      </c>
-      <c r="H30" s="1">
-        <v>1</v>
-      </c>
-      <c r="I30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="2">
-        <v>3400</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -2187,7 +2187,7 @@
       <c r="F31" s="1">
         <v>10081</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="2">
         <v>10000</v>
       </c>
       <c r="H31" s="1">
@@ -2196,7 +2196,7 @@
       <c r="I31" s="1">
         <v>1</v>
       </c>
-      <c r="K31" s="2">
+      <c r="J31" s="3">
         <v>10000</v>
       </c>
       <c r="L31" s="2"/>
@@ -2221,17 +2221,17 @@
       <c r="F32" s="1">
         <v>10081</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3">
         <v>5000</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="2">
-        <v>6600</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -2255,7 +2255,7 @@
       <c r="F33" s="1">
         <v>10081</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="1">
@@ -2264,7 +2264,7 @@
       <c r="I33" s="1">
         <v>1</v>
       </c>
-      <c r="K33" s="2">
+      <c r="J33" s="3">
         <v>0</v>
       </c>
       <c r="L33" s="2"/>
@@ -2289,17 +2289,17 @@
       <c r="F34" s="1">
         <v>10081</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="3">
         <v>2500</v>
-      </c>
-      <c r="H34" s="1">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1">
-        <v>1</v>
-      </c>
-      <c r="K34" s="2">
-        <v>3400</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -2323,7 +2323,7 @@
       <c r="F35" s="1">
         <v>10091</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="2">
         <v>10000</v>
       </c>
       <c r="H35" s="1">
@@ -2332,7 +2332,7 @@
       <c r="I35" s="1">
         <v>1</v>
       </c>
-      <c r="K35" s="2">
+      <c r="J35" s="3">
         <v>10000</v>
       </c>
       <c r="L35" s="2"/>
@@ -2357,17 +2357,17 @@
       <c r="F36" s="1">
         <v>10091</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
         <v>5000</v>
-      </c>
-      <c r="H36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>1</v>
-      </c>
-      <c r="K36" s="2">
-        <v>6600</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -2391,7 +2391,7 @@
       <c r="F37" s="1">
         <v>10091</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="1">
@@ -2400,7 +2400,7 @@
       <c r="I37" s="1">
         <v>1</v>
       </c>
-      <c r="K37" s="2">
+      <c r="J37" s="3">
         <v>0</v>
       </c>
       <c r="L37" s="2"/>
@@ -2425,17 +2425,17 @@
       <c r="F38" s="1">
         <v>10091</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3">
         <v>2500</v>
-      </c>
-      <c r="H38" s="1">
-        <v>1</v>
-      </c>
-      <c r="I38" s="1">
-        <v>1</v>
-      </c>
-      <c r="K38" s="2">
-        <v>3400</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -2459,7 +2459,7 @@
       <c r="F39" s="1">
         <v>10101</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="2">
         <v>10000</v>
       </c>
       <c r="H39" s="1">
@@ -2468,7 +2468,7 @@
       <c r="I39" s="1">
         <v>1</v>
       </c>
-      <c r="K39" s="2">
+      <c r="J39" s="3">
         <v>10000</v>
       </c>
       <c r="L39" s="2"/>
@@ -2493,17 +2493,17 @@
       <c r="F40" s="1">
         <v>10101</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="3">
         <v>5000</v>
-      </c>
-      <c r="H40" s="1">
-        <v>1</v>
-      </c>
-      <c r="I40" s="1">
-        <v>1</v>
-      </c>
-      <c r="K40" s="2">
-        <v>6600</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
@@ -2527,7 +2527,7 @@
       <c r="F41" s="1">
         <v>10101</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="1">
@@ -2536,7 +2536,7 @@
       <c r="I41" s="1">
         <v>1</v>
       </c>
-      <c r="K41" s="2">
+      <c r="J41" s="3">
         <v>0</v>
       </c>
       <c r="L41" s="2"/>
@@ -2561,17 +2561,17 @@
       <c r="F42" s="1">
         <v>10101</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="J42" s="3">
         <v>2500</v>
-      </c>
-      <c r="H42" s="1">
-        <v>1</v>
-      </c>
-      <c r="I42" s="1">
-        <v>1</v>
-      </c>
-      <c r="K42" s="2">
-        <v>3400</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -2595,7 +2595,7 @@
       <c r="F43" s="1">
         <v>20012</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="2">
         <v>10000</v>
       </c>
       <c r="H43" s="1">
@@ -2604,7 +2604,7 @@
       <c r="I43" s="1">
         <v>1</v>
       </c>
-      <c r="K43" s="2">
+      <c r="J43" s="3">
         <v>10000</v>
       </c>
       <c r="L43" s="2"/>
@@ -2629,17 +2629,17 @@
       <c r="F44" s="1">
         <v>20011</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+      <c r="J44" s="3">
         <v>5000</v>
-      </c>
-      <c r="H44" s="1">
-        <v>1</v>
-      </c>
-      <c r="I44" s="1">
-        <v>1</v>
-      </c>
-      <c r="K44" s="2">
-        <v>6600</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -2663,7 +2663,7 @@
       <c r="F45" s="1">
         <v>20011</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="1">
@@ -2672,7 +2672,7 @@
       <c r="I45" s="1">
         <v>1</v>
       </c>
-      <c r="K45" s="2">
+      <c r="J45" s="3">
         <v>0</v>
       </c>
       <c r="L45" s="2"/>
@@ -2697,17 +2697,17 @@
       <c r="F46" s="1">
         <v>20011</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3">
         <v>2500</v>
-      </c>
-      <c r="H46" s="1">
-        <v>1</v>
-      </c>
-      <c r="I46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="2">
-        <v>3400</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -2731,7 +2731,7 @@
       <c r="F47" s="1">
         <v>20022</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="2">
         <v>10000</v>
       </c>
       <c r="H47" s="1">
@@ -2740,7 +2740,7 @@
       <c r="I47" s="1">
         <v>1</v>
       </c>
-      <c r="K47" s="2">
+      <c r="J47" s="3">
         <v>10000</v>
       </c>
       <c r="L47" s="2"/>
@@ -2765,17 +2765,17 @@
       <c r="F48" s="1">
         <v>20021</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1</v>
+      </c>
+      <c r="J48" s="3">
         <v>5000</v>
-      </c>
-      <c r="H48" s="1">
-        <v>1</v>
-      </c>
-      <c r="I48" s="1">
-        <v>1</v>
-      </c>
-      <c r="K48" s="2">
-        <v>6600</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -2799,7 +2799,7 @@
       <c r="F49" s="1">
         <v>20021</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="1">
@@ -2808,7 +2808,7 @@
       <c r="I49" s="1">
         <v>1</v>
       </c>
-      <c r="K49" s="2">
+      <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="2"/>
@@ -2833,17 +2833,17 @@
       <c r="F50" s="1">
         <v>20021</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1</v>
+      </c>
+      <c r="J50" s="3">
         <v>2500</v>
-      </c>
-      <c r="H50" s="1">
-        <v>1</v>
-      </c>
-      <c r="I50" s="1">
-        <v>1</v>
-      </c>
-      <c r="K50" s="2">
-        <v>3400</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -2867,7 +2867,7 @@
       <c r="F51" s="1">
         <v>20032</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="2">
         <v>10000</v>
       </c>
       <c r="H51" s="1">
@@ -2876,7 +2876,7 @@
       <c r="I51" s="1">
         <v>1</v>
       </c>
-      <c r="K51" s="2">
+      <c r="J51" s="3">
         <v>10000</v>
       </c>
       <c r="L51" s="2"/>
@@ -2901,17 +2901,17 @@
       <c r="F52" s="1">
         <v>20031</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1</v>
+      </c>
+      <c r="J52" s="3">
         <v>5000</v>
-      </c>
-      <c r="H52" s="1">
-        <v>1</v>
-      </c>
-      <c r="I52" s="1">
-        <v>1</v>
-      </c>
-      <c r="K52" s="2">
-        <v>6600</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -2935,8 +2935,8 @@
       <c r="F53" s="1">
         <v>20031</v>
       </c>
-      <c r="G53" s="3">
-        <v>0</v>
+      <c r="G53" s="2">
+        <v>5000</v>
       </c>
       <c r="H53" s="1">
         <v>1</v>
@@ -2944,8 +2944,8 @@
       <c r="I53" s="1">
         <v>1</v>
       </c>
-      <c r="K53" s="2">
-        <v>5000</v>
+      <c r="J53" s="3">
+        <v>0</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -2969,17 +2969,17 @@
       <c r="F54" s="1">
         <v>20031</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1</v>
+      </c>
+      <c r="J54" s="3">
         <v>2500</v>
-      </c>
-      <c r="H54" s="1">
-        <v>1</v>
-      </c>
-      <c r="I54" s="1">
-        <v>1</v>
-      </c>
-      <c r="K54" s="2">
-        <v>3400</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -3003,7 +3003,7 @@
       <c r="F55" s="1">
         <v>20042</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="2">
         <v>10000</v>
       </c>
       <c r="H55" s="1">
@@ -3012,7 +3012,7 @@
       <c r="I55" s="1">
         <v>1</v>
       </c>
-      <c r="K55" s="2">
+      <c r="J55" s="3">
         <v>10000</v>
       </c>
       <c r="L55" s="2"/>
@@ -3037,17 +3037,17 @@
       <c r="F56" s="1">
         <v>20041</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1">
+        <v>1</v>
+      </c>
+      <c r="J56" s="3">
         <v>5000</v>
-      </c>
-      <c r="H56" s="1">
-        <v>1</v>
-      </c>
-      <c r="I56" s="1">
-        <v>1</v>
-      </c>
-      <c r="K56" s="2">
-        <v>6600</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -3071,8 +3071,8 @@
       <c r="F57" s="1">
         <v>20041</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
+      <c r="G57" s="2">
+        <v>5000</v>
       </c>
       <c r="H57" s="1">
         <v>1</v>
@@ -3080,8 +3080,8 @@
       <c r="I57" s="1">
         <v>1</v>
       </c>
-      <c r="K57" s="2">
-        <v>5000</v>
+      <c r="J57" s="3">
+        <v>0</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -3105,17 +3105,17 @@
       <c r="F58" s="1">
         <v>20041</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1</v>
+      </c>
+      <c r="I58" s="1">
+        <v>1</v>
+      </c>
+      <c r="J58" s="3">
         <v>2500</v>
-      </c>
-      <c r="H58" s="1">
-        <v>1</v>
-      </c>
-      <c r="I58" s="1">
-        <v>1</v>
-      </c>
-      <c r="K58" s="2">
-        <v>3400</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -3139,7 +3139,7 @@
       <c r="F59" s="1">
         <v>20052</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="2">
         <v>10000</v>
       </c>
       <c r="H59" s="1">
@@ -3148,7 +3148,7 @@
       <c r="I59" s="1">
         <v>1</v>
       </c>
-      <c r="K59" s="2">
+      <c r="J59" s="3">
         <v>10000</v>
       </c>
       <c r="L59" s="2"/>
@@ -3173,17 +3173,17 @@
       <c r="F60" s="1">
         <v>20051</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H60" s="1">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3">
         <v>5000</v>
-      </c>
-      <c r="H60" s="1">
-        <v>1</v>
-      </c>
-      <c r="I60" s="1">
-        <v>1</v>
-      </c>
-      <c r="K60" s="2">
-        <v>6600</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -3207,8 +3207,8 @@
       <c r="F61" s="1">
         <v>20051</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
+      <c r="G61" s="2">
+        <v>5000</v>
       </c>
       <c r="H61" s="1">
         <v>1</v>
@@ -3216,8 +3216,8 @@
       <c r="I61" s="1">
         <v>1</v>
       </c>
-      <c r="K61" s="2">
-        <v>5000</v>
+      <c r="J61" s="3">
+        <v>0</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -3241,17 +3241,17 @@
       <c r="F62" s="1">
         <v>20051</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1</v>
+      </c>
+      <c r="J62" s="3">
         <v>2500</v>
-      </c>
-      <c r="H62" s="1">
-        <v>1</v>
-      </c>
-      <c r="I62" s="1">
-        <v>1</v>
-      </c>
-      <c r="K62" s="2">
-        <v>3400</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -3275,7 +3275,7 @@
       <c r="F63" s="1">
         <v>20062</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63" s="2">
         <v>10000</v>
       </c>
       <c r="H63" s="1">
@@ -3284,7 +3284,7 @@
       <c r="I63" s="1">
         <v>1</v>
       </c>
-      <c r="K63" s="2">
+      <c r="J63" s="3">
         <v>10000</v>
       </c>
       <c r="L63" s="2"/>
@@ -3309,17 +3309,17 @@
       <c r="F64" s="1">
         <v>20061</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1">
+        <v>1</v>
+      </c>
+      <c r="J64" s="3">
         <v>5000</v>
-      </c>
-      <c r="H64" s="1">
-        <v>1</v>
-      </c>
-      <c r="I64" s="1">
-        <v>1</v>
-      </c>
-      <c r="K64" s="2">
-        <v>6600</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -3343,8 +3343,8 @@
       <c r="F65" s="1">
         <v>20061</v>
       </c>
-      <c r="G65" s="3">
-        <v>0</v>
+      <c r="G65" s="2">
+        <v>5000</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
@@ -3352,8 +3352,8 @@
       <c r="I65" s="1">
         <v>1</v>
       </c>
-      <c r="K65" s="2">
-        <v>5000</v>
+      <c r="J65" s="3">
+        <v>0</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -3377,17 +3377,17 @@
       <c r="F66" s="1">
         <v>20061</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+      <c r="J66" s="3">
         <v>2500</v>
-      </c>
-      <c r="H66" s="1">
-        <v>1</v>
-      </c>
-      <c r="I66" s="1">
-        <v>1</v>
-      </c>
-      <c r="K66" s="2">
-        <v>3400</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -3411,7 +3411,7 @@
       <c r="F67" s="1">
         <v>20072</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67" s="2">
         <v>10000</v>
       </c>
       <c r="H67" s="1">
@@ -3420,7 +3420,7 @@
       <c r="I67" s="1">
         <v>1</v>
       </c>
-      <c r="K67" s="2">
+      <c r="J67" s="3">
         <v>10000</v>
       </c>
       <c r="L67" s="2"/>
@@ -3445,17 +3445,17 @@
       <c r="F68" s="1">
         <v>20071</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1</v>
+      </c>
+      <c r="J68" s="3">
         <v>5000</v>
-      </c>
-      <c r="H68" s="1">
-        <v>1</v>
-      </c>
-      <c r="I68" s="1">
-        <v>1</v>
-      </c>
-      <c r="K68" s="2">
-        <v>6600</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -3479,7 +3479,7 @@
       <c r="F69" s="1">
         <v>20071</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="1">
@@ -3488,7 +3488,7 @@
       <c r="I69" s="1">
         <v>1</v>
       </c>
-      <c r="K69" s="2">
+      <c r="J69" s="3">
         <v>0</v>
       </c>
       <c r="L69" s="2"/>
@@ -3513,17 +3513,17 @@
       <c r="F70" s="1">
         <v>20071</v>
       </c>
-      <c r="G70" s="3">
+      <c r="G70" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1</v>
+      </c>
+      <c r="J70" s="3">
         <v>2500</v>
-      </c>
-      <c r="H70" s="1">
-        <v>1</v>
-      </c>
-      <c r="I70" s="1">
-        <v>1</v>
-      </c>
-      <c r="K70" s="2">
-        <v>3400</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -3547,7 +3547,7 @@
       <c r="F71" s="1">
         <v>20082</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71" s="2">
         <v>10000</v>
       </c>
       <c r="H71" s="1">
@@ -3556,7 +3556,7 @@
       <c r="I71" s="1">
         <v>1</v>
       </c>
-      <c r="K71" s="2">
+      <c r="J71" s="3">
         <v>10000</v>
       </c>
       <c r="L71" s="2"/>
@@ -3581,17 +3581,17 @@
       <c r="F72" s="1">
         <v>20081</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1</v>
+      </c>
+      <c r="I72" s="1">
+        <v>1</v>
+      </c>
+      <c r="J72" s="3">
         <v>5000</v>
-      </c>
-      <c r="H72" s="1">
-        <v>1</v>
-      </c>
-      <c r="I72" s="1">
-        <v>1</v>
-      </c>
-      <c r="K72" s="2">
-        <v>6600</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -3615,7 +3615,7 @@
       <c r="F73" s="1">
         <v>20081</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="1">
@@ -3624,7 +3624,7 @@
       <c r="I73" s="1">
         <v>1</v>
       </c>
-      <c r="K73" s="2">
+      <c r="J73" s="3">
         <v>0</v>
       </c>
       <c r="L73" s="2"/>
@@ -3649,17 +3649,17 @@
       <c r="F74" s="1">
         <v>20081</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H74" s="1">
+        <v>1</v>
+      </c>
+      <c r="I74" s="1">
+        <v>1</v>
+      </c>
+      <c r="J74" s="3">
         <v>2500</v>
-      </c>
-      <c r="H74" s="1">
-        <v>1</v>
-      </c>
-      <c r="I74" s="1">
-        <v>1</v>
-      </c>
-      <c r="K74" s="2">
-        <v>3400</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -3683,7 +3683,7 @@
       <c r="F75" s="1">
         <v>30013</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75" s="2">
         <v>10000</v>
       </c>
       <c r="H75" s="1">
@@ -3692,7 +3692,7 @@
       <c r="I75" s="1">
         <v>1</v>
       </c>
-      <c r="K75" s="2">
+      <c r="J75" s="3">
         <v>10000</v>
       </c>
       <c r="L75" s="2"/>
@@ -3717,17 +3717,17 @@
       <c r="F76" s="1">
         <v>30012</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G76" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1</v>
+      </c>
+      <c r="J76" s="3">
         <v>5000</v>
-      </c>
-      <c r="H76" s="1">
-        <v>1</v>
-      </c>
-      <c r="I76" s="1">
-        <v>1</v>
-      </c>
-      <c r="K76" s="2">
-        <v>6600</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -3751,8 +3751,8 @@
       <c r="F77" s="4">
         <v>30012</v>
       </c>
-      <c r="G77" s="3">
-        <v>0</v>
+      <c r="G77" s="5">
+        <v>5000</v>
       </c>
       <c r="H77" s="4">
         <v>1</v>
@@ -3760,8 +3760,8 @@
       <c r="I77" s="4">
         <v>1</v>
       </c>
-      <c r="K77" s="5">
-        <v>5000</v>
+      <c r="J77" s="3">
+        <v>0</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -3785,17 +3785,17 @@
       <c r="F78" s="4">
         <v>30011</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G78" s="5">
+        <v>3400</v>
+      </c>
+      <c r="H78" s="4">
+        <v>1</v>
+      </c>
+      <c r="I78" s="4">
+        <v>1</v>
+      </c>
+      <c r="J78" s="3">
         <v>2500</v>
-      </c>
-      <c r="H78" s="4">
-        <v>1</v>
-      </c>
-      <c r="I78" s="4">
-        <v>1</v>
-      </c>
-      <c r="K78" s="5">
-        <v>3400</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -3819,7 +3819,7 @@
       <c r="F79" s="4">
         <v>30023</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G79" s="5">
         <v>10000</v>
       </c>
       <c r="H79" s="4">
@@ -3828,7 +3828,7 @@
       <c r="I79" s="4">
         <v>1</v>
       </c>
-      <c r="K79" s="5">
+      <c r="J79" s="3">
         <v>10000</v>
       </c>
       <c r="L79" s="2"/>
@@ -3853,8 +3853,8 @@
       <c r="F80" s="4">
         <v>30022</v>
       </c>
-      <c r="G80" s="3">
-        <v>0</v>
+      <c r="G80" s="5">
+        <v>6600</v>
       </c>
       <c r="H80" s="4">
         <v>1</v>
@@ -3862,8 +3862,8 @@
       <c r="I80" s="4">
         <v>1</v>
       </c>
-      <c r="K80" s="5">
-        <v>6600</v>
+      <c r="J80" s="3">
+        <v>0</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -3887,7 +3887,7 @@
       <c r="F81" s="4">
         <v>30022</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G81" s="5">
         <v>0</v>
       </c>
       <c r="H81" s="4">
@@ -3896,7 +3896,7 @@
       <c r="I81" s="4">
         <v>1</v>
       </c>
-      <c r="K81" s="5">
+      <c r="J81" s="3">
         <v>0</v>
       </c>
       <c r="L81" s="2"/>
@@ -3921,8 +3921,8 @@
       <c r="F82" s="4">
         <v>30021</v>
       </c>
-      <c r="G82" s="3">
-        <v>0</v>
+      <c r="G82" s="5">
+        <v>3400</v>
       </c>
       <c r="H82" s="4">
         <v>1</v>
@@ -3930,8 +3930,8 @@
       <c r="I82" s="4">
         <v>1</v>
       </c>
-      <c r="K82" s="5">
-        <v>3400</v>
+      <c r="J82" s="3">
+        <v>0</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -3955,7 +3955,7 @@
       <c r="F83" s="4">
         <v>30033</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="5">
         <v>10000</v>
       </c>
       <c r="H83" s="4">
@@ -3964,7 +3964,7 @@
       <c r="I83" s="4">
         <v>1</v>
       </c>
-      <c r="K83" s="5">
+      <c r="J83" s="3">
         <v>10000</v>
       </c>
       <c r="L83" s="2"/>
@@ -3989,17 +3989,17 @@
       <c r="F84" s="4">
         <v>30032</v>
       </c>
-      <c r="G84" s="3">
+      <c r="G84" s="5">
+        <v>6600</v>
+      </c>
+      <c r="H84" s="4">
+        <v>1</v>
+      </c>
+      <c r="I84" s="4">
+        <v>1</v>
+      </c>
+      <c r="J84" s="3">
         <v>5000</v>
-      </c>
-      <c r="H84" s="4">
-        <v>1</v>
-      </c>
-      <c r="I84" s="4">
-        <v>1</v>
-      </c>
-      <c r="K84" s="5">
-        <v>6600</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -4023,8 +4023,8 @@
       <c r="F85" s="4">
         <v>30032</v>
       </c>
-      <c r="G85" s="3">
-        <v>0</v>
+      <c r="G85" s="5">
+        <v>5000</v>
       </c>
       <c r="H85" s="4">
         <v>1</v>
@@ -4032,8 +4032,8 @@
       <c r="I85" s="4">
         <v>1</v>
       </c>
-      <c r="K85" s="5">
-        <v>5000</v>
+      <c r="J85" s="3">
+        <v>0</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -4057,17 +4057,17 @@
       <c r="F86" s="1">
         <v>30031</v>
       </c>
-      <c r="G86" s="3">
+      <c r="G86" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H86" s="1">
+        <v>1</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1</v>
+      </c>
+      <c r="J86" s="3">
         <v>2500</v>
-      </c>
-      <c r="H86" s="1">
-        <v>1</v>
-      </c>
-      <c r="I86" s="1">
-        <v>1</v>
-      </c>
-      <c r="K86" s="2">
-        <v>3400</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -4091,7 +4091,7 @@
       <c r="F87" s="1">
         <v>30043</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G87" s="2">
         <v>10000</v>
       </c>
       <c r="H87" s="1">
@@ -4100,7 +4100,7 @@
       <c r="I87" s="1">
         <v>1</v>
       </c>
-      <c r="K87" s="2">
+      <c r="J87" s="3">
         <v>10000</v>
       </c>
       <c r="L87" s="2"/>
@@ -4125,17 +4125,17 @@
       <c r="F88" s="1">
         <v>30042</v>
       </c>
-      <c r="G88" s="3">
+      <c r="G88" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H88" s="1">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1">
+        <v>1</v>
+      </c>
+      <c r="J88" s="3">
         <v>5000</v>
-      </c>
-      <c r="H88" s="1">
-        <v>1</v>
-      </c>
-      <c r="I88" s="1">
-        <v>1</v>
-      </c>
-      <c r="K88" s="2">
-        <v>6600</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -4159,7 +4159,7 @@
       <c r="F89" s="1">
         <v>30042</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="2">
         <v>0</v>
       </c>
       <c r="H89" s="1">
@@ -4168,7 +4168,7 @@
       <c r="I89" s="1">
         <v>1</v>
       </c>
-      <c r="K89" s="2">
+      <c r="J89" s="3">
         <v>0</v>
       </c>
       <c r="L89" s="2"/>
@@ -4193,17 +4193,17 @@
       <c r="F90" s="1">
         <v>30041</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G90" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H90" s="1">
+        <v>1</v>
+      </c>
+      <c r="I90" s="1">
+        <v>1</v>
+      </c>
+      <c r="J90" s="3">
         <v>2500</v>
-      </c>
-      <c r="H90" s="1">
-        <v>1</v>
-      </c>
-      <c r="I90" s="1">
-        <v>1</v>
-      </c>
-      <c r="K90" s="2">
-        <v>3400</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -4227,7 +4227,7 @@
       <c r="F91" s="1">
         <v>30053</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="2">
         <v>10000</v>
       </c>
       <c r="H91" s="1">
@@ -4236,7 +4236,7 @@
       <c r="I91" s="1">
         <v>1</v>
       </c>
-      <c r="K91" s="2">
+      <c r="J91" s="3">
         <v>10000</v>
       </c>
       <c r="L91" s="2"/>
@@ -4261,17 +4261,17 @@
       <c r="F92" s="1">
         <v>30052</v>
       </c>
-      <c r="G92" s="3">
+      <c r="G92" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H92" s="1">
+        <v>1</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1</v>
+      </c>
+      <c r="J92" s="3">
         <v>5000</v>
-      </c>
-      <c r="H92" s="1">
-        <v>1</v>
-      </c>
-      <c r="I92" s="1">
-        <v>1</v>
-      </c>
-      <c r="K92" s="2">
-        <v>6600</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -4295,8 +4295,8 @@
       <c r="F93" s="1">
         <v>30052</v>
       </c>
-      <c r="G93" s="3">
-        <v>0</v>
+      <c r="G93" s="2">
+        <v>5000</v>
       </c>
       <c r="H93" s="1">
         <v>1</v>
@@ -4304,8 +4304,8 @@
       <c r="I93" s="1">
         <v>1</v>
       </c>
-      <c r="K93" s="2">
-        <v>5000</v>
+      <c r="J93" s="3">
+        <v>0</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -4329,17 +4329,17 @@
       <c r="F94" s="1">
         <v>30051</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H94" s="1">
+        <v>1</v>
+      </c>
+      <c r="I94" s="1">
+        <v>1</v>
+      </c>
+      <c r="J94" s="3">
         <v>2500</v>
-      </c>
-      <c r="H94" s="1">
-        <v>1</v>
-      </c>
-      <c r="I94" s="1">
-        <v>1</v>
-      </c>
-      <c r="K94" s="2">
-        <v>3400</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -4363,7 +4363,7 @@
       <c r="F95" s="1">
         <v>30063</v>
       </c>
-      <c r="G95" s="3">
+      <c r="G95" s="2">
         <v>10000</v>
       </c>
       <c r="H95" s="1">
@@ -4372,7 +4372,7 @@
       <c r="I95" s="1">
         <v>1</v>
       </c>
-      <c r="K95" s="2">
+      <c r="J95" s="3">
         <v>10000</v>
       </c>
       <c r="L95" s="2"/>
@@ -4397,17 +4397,17 @@
       <c r="F96" s="1">
         <v>30062</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H96" s="1">
+        <v>1</v>
+      </c>
+      <c r="I96" s="1">
+        <v>1</v>
+      </c>
+      <c r="J96" s="3">
         <v>5000</v>
-      </c>
-      <c r="H96" s="1">
-        <v>1</v>
-      </c>
-      <c r="I96" s="1">
-        <v>1</v>
-      </c>
-      <c r="K96" s="2">
-        <v>6600</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -4431,7 +4431,7 @@
       <c r="F97" s="1">
         <v>30062</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="1">
@@ -4440,7 +4440,7 @@
       <c r="I97" s="1">
         <v>1</v>
       </c>
-      <c r="K97" s="2">
+      <c r="J97" s="3">
         <v>0</v>
       </c>
       <c r="L97" s="2"/>
@@ -4465,17 +4465,17 @@
       <c r="F98" s="1">
         <v>30061</v>
       </c>
-      <c r="G98" s="3">
+      <c r="G98" s="2">
+        <v>3400</v>
+      </c>
+      <c r="H98" s="1">
+        <v>1</v>
+      </c>
+      <c r="I98" s="1">
+        <v>1</v>
+      </c>
+      <c r="J98" s="3">
         <v>2500</v>
-      </c>
-      <c r="H98" s="1">
-        <v>1</v>
-      </c>
-      <c r="I98" s="1">
-        <v>1</v>
-      </c>
-      <c r="K98" s="2">
-        <v>3400</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -4499,7 +4499,7 @@
       <c r="F99" s="1">
         <v>40014</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G99" s="2">
         <v>10000</v>
       </c>
       <c r="H99" s="1">
@@ -4508,7 +4508,7 @@
       <c r="I99" s="1">
         <v>1</v>
       </c>
-      <c r="K99" s="2">
+      <c r="J99" s="3">
         <v>10000</v>
       </c>
       <c r="L99" s="2"/>
@@ -4533,17 +4533,17 @@
       <c r="F100" s="1">
         <v>40013</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H100" s="1">
+        <v>1</v>
+      </c>
+      <c r="I100" s="1">
+        <v>1</v>
+      </c>
+      <c r="J100" s="3">
         <v>5000</v>
-      </c>
-      <c r="H100" s="1">
-        <v>1</v>
-      </c>
-      <c r="I100" s="1">
-        <v>1</v>
-      </c>
-      <c r="K100" s="2">
-        <v>6600</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -4567,8 +4567,8 @@
       <c r="F101" s="1">
         <v>40012</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="2">
+        <v>3400</v>
       </c>
       <c r="H101" s="1">
         <v>1</v>
@@ -4576,8 +4576,8 @@
       <c r="I101" s="1">
         <v>1</v>
       </c>
-      <c r="K101" s="2">
-        <v>3400</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -4601,17 +4601,17 @@
       <c r="F102" s="1">
         <v>40011</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102" s="2">
+        <v>0</v>
+      </c>
+      <c r="H102" s="1">
+        <v>1</v>
+      </c>
+      <c r="I102" s="1">
+        <v>1</v>
+      </c>
+      <c r="J102" s="3">
         <v>2500</v>
-      </c>
-      <c r="H102" s="1">
-        <v>1</v>
-      </c>
-      <c r="I102" s="1">
-        <v>1</v>
-      </c>
-      <c r="K102" s="2">
-        <v>0</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -4635,7 +4635,7 @@
       <c r="F103" s="1">
         <v>40024</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G103" s="2">
         <v>10000</v>
       </c>
       <c r="H103" s="1">
@@ -4644,7 +4644,7 @@
       <c r="I103" s="1">
         <v>1</v>
       </c>
-      <c r="K103" s="2">
+      <c r="J103" s="3">
         <v>10000</v>
       </c>
       <c r="L103" s="2"/>
@@ -4669,17 +4669,17 @@
       <c r="F104" s="1">
         <v>40023</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G104" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H104" s="1">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1">
+        <v>1</v>
+      </c>
+      <c r="J104" s="3">
         <v>5000</v>
-      </c>
-      <c r="H104" s="1">
-        <v>1</v>
-      </c>
-      <c r="I104" s="1">
-        <v>1</v>
-      </c>
-      <c r="K104" s="2">
-        <v>6600</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -4703,8 +4703,8 @@
       <c r="F105" s="1">
         <v>40022</v>
       </c>
-      <c r="G105" s="3">
-        <v>0</v>
+      <c r="G105" s="2">
+        <v>3400</v>
       </c>
       <c r="H105" s="1">
         <v>1</v>
@@ -4712,8 +4712,8 @@
       <c r="I105" s="1">
         <v>1</v>
       </c>
-      <c r="K105" s="2">
-        <v>3400</v>
+      <c r="J105" s="3">
+        <v>0</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -4737,17 +4737,17 @@
       <c r="F106" s="1">
         <v>40021</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G106" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H106" s="1">
+        <v>1</v>
+      </c>
+      <c r="I106" s="1">
+        <v>1</v>
+      </c>
+      <c r="J106" s="3">
         <v>2500</v>
-      </c>
-      <c r="H106" s="1">
-        <v>1</v>
-      </c>
-      <c r="I106" s="1">
-        <v>1</v>
-      </c>
-      <c r="K106" s="2">
-        <v>5000</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -4771,7 +4771,7 @@
       <c r="F107" s="1">
         <v>40034</v>
       </c>
-      <c r="G107" s="3">
+      <c r="G107" s="2">
         <v>10000</v>
       </c>
       <c r="H107" s="1">
@@ -4780,7 +4780,7 @@
       <c r="I107" s="1">
         <v>1</v>
       </c>
-      <c r="K107" s="2">
+      <c r="J107" s="3">
         <v>10000</v>
       </c>
       <c r="L107" s="2"/>
@@ -4805,17 +4805,17 @@
       <c r="F108" s="1">
         <v>40033</v>
       </c>
-      <c r="G108" s="3">
+      <c r="G108" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H108" s="1">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1">
+        <v>1</v>
+      </c>
+      <c r="J108" s="3">
         <v>5000</v>
-      </c>
-      <c r="H108" s="1">
-        <v>1</v>
-      </c>
-      <c r="I108" s="1">
-        <v>1</v>
-      </c>
-      <c r="K108" s="2">
-        <v>6600</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -4839,8 +4839,8 @@
       <c r="F109" s="1">
         <v>40032</v>
       </c>
-      <c r="G109" s="3">
-        <v>0</v>
+      <c r="G109" s="2">
+        <v>3400</v>
       </c>
       <c r="H109" s="1">
         <v>1</v>
@@ -4848,8 +4848,8 @@
       <c r="I109" s="1">
         <v>1</v>
       </c>
-      <c r="K109" s="2">
-        <v>3400</v>
+      <c r="J109" s="3">
+        <v>0</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -4873,17 +4873,17 @@
       <c r="F110" s="1">
         <v>40031</v>
       </c>
-      <c r="G110" s="3">
+      <c r="G110" s="2">
+        <v>0</v>
+      </c>
+      <c r="H110" s="1">
+        <v>1</v>
+      </c>
+      <c r="I110" s="1">
+        <v>1</v>
+      </c>
+      <c r="J110" s="3">
         <v>2500</v>
-      </c>
-      <c r="H110" s="1">
-        <v>1</v>
-      </c>
-      <c r="I110" s="1">
-        <v>1</v>
-      </c>
-      <c r="K110" s="2">
-        <v>0</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -4907,7 +4907,7 @@
       <c r="F111" s="1">
         <v>40044</v>
       </c>
-      <c r="G111" s="3">
+      <c r="G111" s="2">
         <v>10000</v>
       </c>
       <c r="H111" s="1">
@@ -4916,7 +4916,7 @@
       <c r="I111" s="1">
         <v>1</v>
       </c>
-      <c r="K111" s="2">
+      <c r="J111" s="3">
         <v>10000</v>
       </c>
       <c r="L111" s="2"/>
@@ -4941,17 +4941,17 @@
       <c r="F112" s="1">
         <v>40043</v>
       </c>
-      <c r="G112" s="3">
+      <c r="G112" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H112" s="1">
+        <v>1</v>
+      </c>
+      <c r="I112" s="1">
+        <v>1</v>
+      </c>
+      <c r="J112" s="3">
         <v>5000</v>
-      </c>
-      <c r="H112" s="1">
-        <v>1</v>
-      </c>
-      <c r="I112" s="1">
-        <v>1</v>
-      </c>
-      <c r="K112" s="2">
-        <v>6600</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -4975,8 +4975,8 @@
       <c r="F113" s="1">
         <v>40042</v>
       </c>
-      <c r="G113" s="3">
-        <v>0</v>
+      <c r="G113" s="2">
+        <v>3400</v>
       </c>
       <c r="H113" s="1">
         <v>1</v>
@@ -4984,8 +4984,8 @@
       <c r="I113" s="1">
         <v>1</v>
       </c>
-      <c r="K113" s="2">
-        <v>3400</v>
+      <c r="J113" s="3">
+        <v>0</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -5009,17 +5009,17 @@
       <c r="F114" s="1">
         <v>40041</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G114" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H114" s="1">
+        <v>1</v>
+      </c>
+      <c r="I114" s="1">
+        <v>1</v>
+      </c>
+      <c r="J114" s="3">
         <v>2500</v>
-      </c>
-      <c r="H114" s="1">
-        <v>1</v>
-      </c>
-      <c r="I114" s="1">
-        <v>1</v>
-      </c>
-      <c r="K114" s="2">
-        <v>5000</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -5043,7 +5043,7 @@
       <c r="F115" s="1">
         <v>40054</v>
       </c>
-      <c r="G115" s="3">
+      <c r="G115" s="2">
         <v>10000</v>
       </c>
       <c r="H115" s="1">
@@ -5052,7 +5052,7 @@
       <c r="I115" s="1">
         <v>1</v>
       </c>
-      <c r="K115" s="2">
+      <c r="J115" s="3">
         <v>10000</v>
       </c>
       <c r="L115" s="2"/>
@@ -5077,17 +5077,17 @@
       <c r="F116" s="1">
         <v>40053</v>
       </c>
-      <c r="G116" s="3">
+      <c r="G116" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H116" s="1">
+        <v>1</v>
+      </c>
+      <c r="I116" s="1">
+        <v>1</v>
+      </c>
+      <c r="J116" s="3">
         <v>5000</v>
-      </c>
-      <c r="H116" s="1">
-        <v>1</v>
-      </c>
-      <c r="I116" s="1">
-        <v>1</v>
-      </c>
-      <c r="K116" s="2">
-        <v>6600</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -5111,8 +5111,8 @@
       <c r="F117" s="1">
         <v>40052</v>
       </c>
-      <c r="G117" s="3">
-        <v>0</v>
+      <c r="G117" s="2">
+        <v>3400</v>
       </c>
       <c r="H117" s="1">
         <v>1</v>
@@ -5120,8 +5120,8 @@
       <c r="I117" s="1">
         <v>1</v>
       </c>
-      <c r="K117" s="2">
-        <v>3400</v>
+      <c r="J117" s="3">
+        <v>0</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -5145,17 +5145,17 @@
       <c r="F118" s="1">
         <v>40051</v>
       </c>
-      <c r="G118" s="3">
+      <c r="G118" s="2">
+        <v>0</v>
+      </c>
+      <c r="H118" s="1">
+        <v>1</v>
+      </c>
+      <c r="I118" s="1">
+        <v>1</v>
+      </c>
+      <c r="J118" s="3">
         <v>2500</v>
-      </c>
-      <c r="H118" s="1">
-        <v>1</v>
-      </c>
-      <c r="I118" s="1">
-        <v>1</v>
-      </c>
-      <c r="K118" s="2">
-        <v>0</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -5179,7 +5179,7 @@
       <c r="F119" s="1">
         <v>50015</v>
       </c>
-      <c r="G119" s="3">
+      <c r="G119" s="2">
         <v>10000</v>
       </c>
       <c r="H119" s="1">
@@ -5188,7 +5188,7 @@
       <c r="I119" s="1">
         <v>1</v>
       </c>
-      <c r="K119" s="2">
+      <c r="J119" s="3">
         <v>10000</v>
       </c>
       <c r="L119" s="2"/>
@@ -5213,17 +5213,17 @@
       <c r="F120" s="1">
         <v>50014</v>
       </c>
-      <c r="G120" s="3">
+      <c r="G120" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H120" s="1">
+        <v>1</v>
+      </c>
+      <c r="I120" s="1">
+        <v>1</v>
+      </c>
+      <c r="J120" s="3">
         <v>5000</v>
-      </c>
-      <c r="H120" s="1">
-        <v>1</v>
-      </c>
-      <c r="I120" s="1">
-        <v>1</v>
-      </c>
-      <c r="K120" s="2">
-        <v>6600</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -5247,8 +5247,8 @@
       <c r="F121" s="1">
         <v>50013</v>
       </c>
-      <c r="G121" s="3">
-        <v>0</v>
+      <c r="G121" s="2">
+        <v>3400</v>
       </c>
       <c r="H121" s="1">
         <v>1</v>
@@ -5256,8 +5256,8 @@
       <c r="I121" s="1">
         <v>1</v>
       </c>
-      <c r="K121" s="2">
-        <v>3400</v>
+      <c r="J121" s="3">
+        <v>0</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -5281,17 +5281,17 @@
       <c r="F122" s="1">
         <v>50012</v>
       </c>
-      <c r="G122" s="3">
+      <c r="G122" s="2">
+        <v>0</v>
+      </c>
+      <c r="H122" s="1">
+        <v>1</v>
+      </c>
+      <c r="I122" s="1">
+        <v>1</v>
+      </c>
+      <c r="J122" s="3">
         <v>2500</v>
-      </c>
-      <c r="H122" s="1">
-        <v>1</v>
-      </c>
-      <c r="I122" s="1">
-        <v>1</v>
-      </c>
-      <c r="K122" s="2">
-        <v>0</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -5315,7 +5315,7 @@
       <c r="F123" s="6">
         <v>50025</v>
       </c>
-      <c r="G123" s="3">
+      <c r="G123" s="2">
         <v>10000</v>
       </c>
       <c r="H123" s="1">
@@ -5324,7 +5324,7 @@
       <c r="I123" s="1">
         <v>1</v>
       </c>
-      <c r="K123" s="2">
+      <c r="J123" s="3">
         <v>10000</v>
       </c>
       <c r="L123" s="2"/>
@@ -5349,17 +5349,17 @@
       <c r="F124" s="6">
         <v>50024</v>
       </c>
-      <c r="G124" s="3">
+      <c r="G124" s="2">
+        <v>0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>1</v>
+      </c>
+      <c r="I124" s="1">
+        <v>1</v>
+      </c>
+      <c r="J124" s="3">
         <v>5000</v>
-      </c>
-      <c r="H124" s="1">
-        <v>1</v>
-      </c>
-      <c r="I124" s="1">
-        <v>1</v>
-      </c>
-      <c r="K124" s="2">
-        <v>0</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -5383,7 +5383,7 @@
       <c r="F125" s="6">
         <v>50023</v>
       </c>
-      <c r="G125" s="3">
+      <c r="G125" s="2">
         <v>0</v>
       </c>
       <c r="H125" s="1">
@@ -5392,7 +5392,7 @@
       <c r="I125" s="1">
         <v>1</v>
       </c>
-      <c r="K125" s="2">
+      <c r="J125" s="3">
         <v>0</v>
       </c>
       <c r="L125" s="2"/>
@@ -5417,17 +5417,17 @@
       <c r="F126" s="6">
         <v>50022</v>
       </c>
-      <c r="G126" s="3">
+      <c r="G126" s="2">
+        <v>0</v>
+      </c>
+      <c r="H126" s="1">
+        <v>1</v>
+      </c>
+      <c r="I126" s="1">
+        <v>1</v>
+      </c>
+      <c r="J126" s="3">
         <v>2500</v>
-      </c>
-      <c r="H126" s="1">
-        <v>1</v>
-      </c>
-      <c r="I126" s="1">
-        <v>1</v>
-      </c>
-      <c r="K126" s="2">
-        <v>0</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -5451,7 +5451,7 @@
       <c r="F127" s="1">
         <v>60016</v>
       </c>
-      <c r="G127" s="3">
+      <c r="G127" s="2">
         <v>10000</v>
       </c>
       <c r="H127" s="1">
@@ -5460,7 +5460,7 @@
       <c r="I127" s="1">
         <v>1</v>
       </c>
-      <c r="K127" s="2">
+      <c r="J127" s="3">
         <v>10000</v>
       </c>
       <c r="L127" s="2"/>
@@ -5485,17 +5485,17 @@
       <c r="F128" s="1">
         <v>60015</v>
       </c>
-      <c r="G128" s="3">
+      <c r="G128" s="2">
+        <v>6600</v>
+      </c>
+      <c r="H128" s="1">
+        <v>1</v>
+      </c>
+      <c r="I128" s="1">
+        <v>1</v>
+      </c>
+      <c r="J128" s="3">
         <v>5000</v>
-      </c>
-      <c r="H128" s="1">
-        <v>1</v>
-      </c>
-      <c r="I128" s="1">
-        <v>1</v>
-      </c>
-      <c r="K128" s="2">
-        <v>6600</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -5519,8 +5519,8 @@
       <c r="F129" s="1">
         <v>60014</v>
       </c>
-      <c r="G129" s="3">
-        <v>0</v>
+      <c r="G129" s="2">
+        <v>3400</v>
       </c>
       <c r="H129" s="1">
         <v>1</v>
@@ -5528,8 +5528,8 @@
       <c r="I129" s="1">
         <v>1</v>
       </c>
-      <c r="K129" s="2">
-        <v>3400</v>
+      <c r="J129" s="3">
+        <v>0</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -5553,17 +5553,17 @@
       <c r="F130" s="1">
         <v>60013</v>
       </c>
-      <c r="G130" s="3">
+      <c r="G130" s="2">
+        <v>0</v>
+      </c>
+      <c r="H130" s="1">
+        <v>1</v>
+      </c>
+      <c r="I130" s="1">
+        <v>1</v>
+      </c>
+      <c r="J130" s="3">
         <v>2500</v>
-      </c>
-      <c r="H130" s="1">
-        <v>1</v>
-      </c>
-      <c r="I130" s="1">
-        <v>1</v>
-      </c>
-      <c r="K130" s="2">
-        <v>0</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -5572,7 +5572,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="G1:G130" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="G3:G114">
+  <conditionalFormatting sqref="J3:J114">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($D3,2)=1</formula>
     </cfRule>
